--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DC68D66-A848-4975-AC41-FB9988B01B70}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B3D75B-B1F8-4521-B37A-32B66F9E735B}"/>
   <bookViews>
-    <workbookView xWindow="11625" yWindow="1110" windowWidth="11850" windowHeight="12315" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15330" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2531,6 +2531,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15349,7 +15353,7 @@
         <v>52</v>
       </c>
       <c r="I384" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="R384" t="s">
         <v>605</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56919962-C5FC-4BA4-A594-A63BD748691E}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC158553-BEF5-49ED-951A-FF2E041CA286}"/>
   <bookViews>
-    <workbookView xWindow="8715" yWindow="1545" windowWidth="16155" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2558,6 +2558,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13750,7 +13754,7 @@
         <v>76</v>
       </c>
       <c r="E339">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="F339" t="s">
         <v>37</v>
@@ -16826,7 +16830,7 @@
         <v>188</v>
       </c>
       <c r="E431">
-        <v>6680</v>
+        <v>3675</v>
       </c>
       <c r="F431" t="s">
         <v>26</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC158553-BEF5-49ED-951A-FF2E041CA286}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FE5AB7-DF7D-4394-962D-828EB8FD09EA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
@@ -13518,7 +13518,7 @@
         <v>742</v>
       </c>
       <c r="D332">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E332" t="s">
         <v>77</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FE5AB7-DF7D-4394-962D-828EB8FD09EA}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{116ED84F-C82B-4D99-93FD-184ACFC340C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
@@ -2301,19 +2301,6 @@
     <t>光月トキ</t>
   </si>
   <si>
-    <t>黒炭せみ丸</t>
-  </si>
-  <si>
-    <t>黒炭ひぐらし</t>
-  </si>
-  <si>
-    <t>黒炭ひぐらし（胡坐時）</t>
-    <rPh sb="7" eb="10">
-      <t>アグラジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>うるティ</t>
   </si>
   <si>
@@ -2493,6 +2480,21 @@
   </si>
   <si>
     <t>モンキー・D・ルフィ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭せみ丸（胡坐時）</t>
+    <rPh sb="6" eb="9">
+      <t>アグラジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒炭ひぐらし</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2920,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
@@ -2928,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2958,7 +2960,7 @@
         <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
@@ -2996,7 +2998,7 @@
         <v>22</v>
       </c>
       <c r="R3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -3040,7 +3042,7 @@
         <v>29</v>
       </c>
       <c r="R4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
@@ -3072,7 +3074,7 @@
         <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.4">
@@ -3110,7 +3112,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.4">
@@ -3157,7 +3159,7 @@
         <v>44</v>
       </c>
       <c r="R7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
@@ -3189,7 +3191,7 @@
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.4">
@@ -3224,7 +3226,7 @@
         <v>28</v>
       </c>
       <c r="R9" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.4">
@@ -3256,7 +3258,7 @@
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.4">
@@ -3288,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="R11" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.4">
@@ -3320,7 +3322,7 @@
         <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
@@ -3352,7 +3354,7 @@
         <v>20</v>
       </c>
       <c r="R13" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
@@ -3454,7 +3456,7 @@
         <v>28</v>
       </c>
       <c r="R16" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
@@ -3492,7 +3494,7 @@
         <v>75</v>
       </c>
       <c r="R17" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.4">
@@ -3533,7 +3535,7 @@
         <v>42</v>
       </c>
       <c r="R18" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
@@ -3574,7 +3576,7 @@
         <v>42</v>
       </c>
       <c r="R19" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.4">
@@ -3606,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="R20" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
@@ -3644,7 +3646,7 @@
         <v>74</v>
       </c>
       <c r="R21" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.4">
@@ -3676,7 +3678,7 @@
         <v>20</v>
       </c>
       <c r="R22" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.4">
@@ -3711,7 +3713,7 @@
         <v>74</v>
       </c>
       <c r="R23" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.4">
@@ -3743,7 +3745,7 @@
         <v>20</v>
       </c>
       <c r="R24" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.4">
@@ -3775,7 +3777,7 @@
         <v>20</v>
       </c>
       <c r="R25" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.4">
@@ -3807,7 +3809,7 @@
         <v>34</v>
       </c>
       <c r="R26" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.4">
@@ -3842,7 +3844,7 @@
         <v>21</v>
       </c>
       <c r="R27" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.4">
@@ -3877,7 +3879,7 @@
         <v>74</v>
       </c>
       <c r="R28" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.4">
@@ -3912,7 +3914,7 @@
         <v>21</v>
       </c>
       <c r="R29" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.4">
@@ -3947,7 +3949,7 @@
         <v>92</v>
       </c>
       <c r="R30" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.4">
@@ -3979,7 +3981,7 @@
         <v>20</v>
       </c>
       <c r="R31" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.4">
@@ -4011,7 +4013,7 @@
         <v>20</v>
       </c>
       <c r="R32" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
@@ -4040,7 +4042,7 @@
         <v>20</v>
       </c>
       <c r="R33" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.4">
@@ -4069,7 +4071,7 @@
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.4">
@@ -4101,7 +4103,7 @@
         <v>20</v>
       </c>
       <c r="R35" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.4">
@@ -4133,7 +4135,7 @@
         <v>20</v>
       </c>
       <c r="R36" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.4">
@@ -4165,7 +4167,7 @@
         <v>20</v>
       </c>
       <c r="R37" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.4">
@@ -4197,7 +4199,7 @@
         <v>20</v>
       </c>
       <c r="R38" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.4">
@@ -4229,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="R39" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.4">
@@ -4261,7 +4263,7 @@
         <v>20</v>
       </c>
       <c r="R40" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.4">
@@ -4293,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="R41" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.4">
@@ -4322,7 +4324,7 @@
         <v>20</v>
       </c>
       <c r="R42" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.4">
@@ -4354,7 +4356,7 @@
         <v>34</v>
       </c>
       <c r="R43" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.4">
@@ -4386,7 +4388,7 @@
         <v>20</v>
       </c>
       <c r="R44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.4">
@@ -4418,7 +4420,7 @@
         <v>20</v>
       </c>
       <c r="R45" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.4">
@@ -4450,7 +4452,7 @@
         <v>20</v>
       </c>
       <c r="R46" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.4">
@@ -4482,7 +4484,7 @@
         <v>20</v>
       </c>
       <c r="R47" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.4">
@@ -4514,7 +4516,7 @@
         <v>20</v>
       </c>
       <c r="R48" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.4">
@@ -4546,7 +4548,7 @@
         <v>20</v>
       </c>
       <c r="R49" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.4">
@@ -4575,7 +4577,7 @@
         <v>20</v>
       </c>
       <c r="R50" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.4">
@@ -4604,7 +4606,7 @@
         <v>20</v>
       </c>
       <c r="R51" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.4">
@@ -4612,13 +4614,13 @@
         <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C52">
         <v>40</v>
       </c>
       <c r="D52" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E52">
         <v>200</v>
@@ -4627,7 +4629,7 @@
         <v>77</v>
       </c>
       <c r="G52" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
@@ -4659,7 +4661,7 @@
         <v>20</v>
       </c>
       <c r="R53" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.4">
@@ -4688,7 +4690,7 @@
         <v>20</v>
       </c>
       <c r="R54" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.4">
@@ -4717,7 +4719,7 @@
         <v>20</v>
       </c>
       <c r="R55" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.4">
@@ -4746,7 +4748,7 @@
         <v>20</v>
       </c>
       <c r="R56" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.4">
@@ -4775,7 +4777,7 @@
         <v>20</v>
       </c>
       <c r="R57" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.4">
@@ -4804,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="R58" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.4">
@@ -4836,7 +4838,7 @@
         <v>20</v>
       </c>
       <c r="R59" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.4">
@@ -4868,7 +4870,7 @@
         <v>20</v>
       </c>
       <c r="R60" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.4">
@@ -4900,7 +4902,7 @@
         <v>34</v>
       </c>
       <c r="R61" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.4">
@@ -4932,7 +4934,7 @@
         <v>20</v>
       </c>
       <c r="R62" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.4">
@@ -4961,7 +4963,7 @@
         <v>20</v>
       </c>
       <c r="R63" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.4">
@@ -4993,7 +4995,7 @@
         <v>20</v>
       </c>
       <c r="R64" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.4">
@@ -5025,7 +5027,7 @@
         <v>20</v>
       </c>
       <c r="R65" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.4">
@@ -5057,7 +5059,7 @@
         <v>34</v>
       </c>
       <c r="R66" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.4">
@@ -5086,7 +5088,7 @@
         <v>20</v>
       </c>
       <c r="R67" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.4">
@@ -5118,7 +5120,7 @@
         <v>20</v>
       </c>
       <c r="R68" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.4">
@@ -5147,7 +5149,7 @@
         <v>20</v>
       </c>
       <c r="R69" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.4">
@@ -5176,7 +5178,7 @@
         <v>34</v>
       </c>
       <c r="R70" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.4">
@@ -5214,7 +5216,7 @@
         <v>74</v>
       </c>
       <c r="R71" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.4">
@@ -5243,7 +5245,7 @@
         <v>20</v>
       </c>
       <c r="R72" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.4">
@@ -5272,7 +5274,7 @@
         <v>20</v>
       </c>
       <c r="R73" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.4">
@@ -5307,7 +5309,7 @@
         <v>75</v>
       </c>
       <c r="R74" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.4">
@@ -5339,7 +5341,7 @@
         <v>20</v>
       </c>
       <c r="R75" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.4">
@@ -5368,7 +5370,7 @@
         <v>20</v>
       </c>
       <c r="R76" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.4">
@@ -5397,7 +5399,7 @@
         <v>34</v>
       </c>
       <c r="R77" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.4">
@@ -5429,7 +5431,7 @@
         <v>20</v>
       </c>
       <c r="R78" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.4">
@@ -5461,7 +5463,7 @@
         <v>20</v>
       </c>
       <c r="R79" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.4">
@@ -5490,7 +5492,7 @@
         <v>20</v>
       </c>
       <c r="R80" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.4">
@@ -5519,7 +5521,7 @@
         <v>34</v>
       </c>
       <c r="R81" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.4">
@@ -5551,7 +5553,7 @@
         <v>20</v>
       </c>
       <c r="R82" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.4">
@@ -5586,7 +5588,7 @@
         <v>75</v>
       </c>
       <c r="R83" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.4">
@@ -5618,7 +5620,7 @@
         <v>20</v>
       </c>
       <c r="R84" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.4">
@@ -5650,7 +5652,7 @@
         <v>20</v>
       </c>
       <c r="R85" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.4">
@@ -5682,7 +5684,7 @@
         <v>20</v>
       </c>
       <c r="R86" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.4">
@@ -5714,7 +5716,7 @@
         <v>34</v>
       </c>
       <c r="R87" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.4">
@@ -5746,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="R88" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.4">
@@ -5778,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="R89" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.4">
@@ -5810,7 +5812,7 @@
         <v>20</v>
       </c>
       <c r="R90" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.4">
@@ -5848,7 +5850,7 @@
         <v>92</v>
       </c>
       <c r="R91" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.4">
@@ -5877,7 +5879,7 @@
         <v>165</v>
       </c>
       <c r="R92" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.4">
@@ -5906,7 +5908,7 @@
         <v>20</v>
       </c>
       <c r="R93" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.4">
@@ -5944,7 +5946,7 @@
         <v>28</v>
       </c>
       <c r="R94" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.4">
@@ -5982,7 +5984,7 @@
         <v>28</v>
       </c>
       <c r="R95" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.4">
@@ -6011,7 +6013,7 @@
         <v>34</v>
       </c>
       <c r="R96" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.4">
@@ -6040,7 +6042,7 @@
         <v>20</v>
       </c>
       <c r="R97" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.4">
@@ -6069,7 +6071,7 @@
         <v>34</v>
       </c>
       <c r="R98" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.4">
@@ -6098,7 +6100,7 @@
         <v>20</v>
       </c>
       <c r="R99" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.4">
@@ -6130,7 +6132,7 @@
         <v>20</v>
       </c>
       <c r="R100" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.4">
@@ -6168,7 +6170,7 @@
         <v>28</v>
       </c>
       <c r="R101" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.4">
@@ -6200,7 +6202,7 @@
         <v>20</v>
       </c>
       <c r="R102" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.4">
@@ -6232,7 +6234,7 @@
         <v>20</v>
       </c>
       <c r="R103" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.4">
@@ -6264,7 +6266,7 @@
         <v>20</v>
       </c>
       <c r="R104" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.4">
@@ -6296,7 +6298,7 @@
         <v>20</v>
       </c>
       <c r="R105" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.4">
@@ -6328,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="R106" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.4">
@@ -6360,7 +6362,7 @@
         <v>20</v>
       </c>
       <c r="R107" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.4">
@@ -6392,7 +6394,7 @@
         <v>20</v>
       </c>
       <c r="R108" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.4">
@@ -6424,7 +6426,7 @@
         <v>20</v>
       </c>
       <c r="R109" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.4">
@@ -6453,7 +6455,7 @@
         <v>34</v>
       </c>
       <c r="R110" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.4">
@@ -6482,7 +6484,7 @@
         <v>20</v>
       </c>
       <c r="R111" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.4">
@@ -6514,7 +6516,7 @@
         <v>20</v>
       </c>
       <c r="R112" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.4">
@@ -6546,7 +6548,7 @@
         <v>20</v>
       </c>
       <c r="R113" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.4">
@@ -6575,7 +6577,7 @@
         <v>20</v>
       </c>
       <c r="R114" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.4">
@@ -6604,7 +6606,7 @@
         <v>20</v>
       </c>
       <c r="R115" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.4">
@@ -6636,7 +6638,7 @@
         <v>194</v>
       </c>
       <c r="R116" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.4">
@@ -6665,7 +6667,7 @@
         <v>20</v>
       </c>
       <c r="R117" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.4">
@@ -6700,7 +6702,7 @@
         <v>43</v>
       </c>
       <c r="R118" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.4">
@@ -6735,7 +6737,7 @@
         <v>21</v>
       </c>
       <c r="R119" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.4">
@@ -6764,7 +6766,7 @@
         <v>20</v>
       </c>
       <c r="R120" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.4">
@@ -6796,7 +6798,7 @@
         <v>20</v>
       </c>
       <c r="R121" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.4">
@@ -6825,7 +6827,7 @@
         <v>20</v>
       </c>
       <c r="R122" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.4">
@@ -6854,7 +6856,7 @@
         <v>20</v>
       </c>
       <c r="R123" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.4">
@@ -6892,7 +6894,7 @@
         <v>28</v>
       </c>
       <c r="R124" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.4">
@@ -6921,7 +6923,7 @@
         <v>20</v>
       </c>
       <c r="R125" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.4">
@@ -6950,7 +6952,7 @@
         <v>20</v>
       </c>
       <c r="R126" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.4">
@@ -6979,7 +6981,7 @@
         <v>34</v>
       </c>
       <c r="R127" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.4">
@@ -7014,7 +7016,7 @@
         <v>21</v>
       </c>
       <c r="R128" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.4">
@@ -7049,7 +7051,7 @@
         <v>92</v>
       </c>
       <c r="R129" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.4">
@@ -7084,7 +7086,7 @@
         <v>43</v>
       </c>
       <c r="R130" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.4">
@@ -7116,7 +7118,7 @@
         <v>20</v>
       </c>
       <c r="R131" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.4">
@@ -7151,7 +7153,7 @@
         <v>28</v>
       </c>
       <c r="R132" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.4">
@@ -7183,7 +7185,7 @@
         <v>20</v>
       </c>
       <c r="R133" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.4">
@@ -7215,7 +7217,7 @@
         <v>20</v>
       </c>
       <c r="R134" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.4">
@@ -7247,7 +7249,7 @@
         <v>20</v>
       </c>
       <c r="R135" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.4">
@@ -7279,7 +7281,7 @@
         <v>20</v>
       </c>
       <c r="R136" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.4">
@@ -7311,7 +7313,7 @@
         <v>34</v>
       </c>
       <c r="R137" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.4">
@@ -7343,7 +7345,7 @@
         <v>20</v>
       </c>
       <c r="R138" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.4">
@@ -7375,7 +7377,7 @@
         <v>20</v>
       </c>
       <c r="R139" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.4">
@@ -7407,7 +7409,7 @@
         <v>20</v>
       </c>
       <c r="R140" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.4">
@@ -7439,7 +7441,7 @@
         <v>20</v>
       </c>
       <c r="R141" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.4">
@@ -7477,7 +7479,7 @@
         <v>43</v>
       </c>
       <c r="R142" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.4">
@@ -7512,7 +7514,7 @@
         <v>43</v>
       </c>
       <c r="R143" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.4">
@@ -7544,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="R144" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.4">
@@ -7576,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="R145" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.4">
@@ -7608,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="R146" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.4">
@@ -7637,7 +7639,7 @@
         <v>20</v>
       </c>
       <c r="R147" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.4">
@@ -7666,7 +7668,7 @@
         <v>20</v>
       </c>
       <c r="R148" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.4">
@@ -7698,7 +7700,7 @@
         <v>20</v>
       </c>
       <c r="R149" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.4">
@@ -7733,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="R150" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.4">
@@ -7768,7 +7770,7 @@
         <v>194</v>
       </c>
       <c r="R151" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.4">
@@ -7800,7 +7802,7 @@
         <v>20</v>
       </c>
       <c r="R152" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.4">
@@ -7829,7 +7831,7 @@
         <v>20</v>
       </c>
       <c r="R153" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.4">
@@ -7861,7 +7863,7 @@
         <v>20</v>
       </c>
       <c r="R154" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.4">
@@ -7896,7 +7898,7 @@
         <v>248</v>
       </c>
       <c r="R155" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.4">
@@ -7928,7 +7930,7 @@
         <v>20</v>
       </c>
       <c r="R156" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.4">
@@ -7957,7 +7959,7 @@
         <v>20</v>
       </c>
       <c r="R157" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.4">
@@ -7986,7 +7988,7 @@
         <v>20</v>
       </c>
       <c r="R158" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.4">
@@ -8018,7 +8020,7 @@
         <v>20</v>
       </c>
       <c r="R159" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.4">
@@ -8053,7 +8055,7 @@
         <v>248</v>
       </c>
       <c r="R160" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.4">
@@ -8088,7 +8090,7 @@
         <v>44</v>
       </c>
       <c r="R161" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.4">
@@ -8120,7 +8122,7 @@
         <v>20</v>
       </c>
       <c r="R162" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.4">
@@ -8149,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="R163" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="164" spans="1:18" x14ac:dyDescent="0.4">
@@ -8184,7 +8186,7 @@
         <v>43</v>
       </c>
       <c r="R164" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.4">
@@ -8216,7 +8218,7 @@
         <v>21</v>
       </c>
       <c r="R165" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="166" spans="1:18" x14ac:dyDescent="0.4">
@@ -8248,7 +8250,7 @@
         <v>20</v>
       </c>
       <c r="R166" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.4">
@@ -8277,7 +8279,7 @@
         <v>20</v>
       </c>
       <c r="R167" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.4">
@@ -8306,7 +8308,7 @@
         <v>20</v>
       </c>
       <c r="R168" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.4">
@@ -8335,7 +8337,7 @@
         <v>20</v>
       </c>
       <c r="R169" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.4">
@@ -8364,7 +8366,7 @@
         <v>20</v>
       </c>
       <c r="R170" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.4">
@@ -8393,7 +8395,7 @@
         <v>20</v>
       </c>
       <c r="R171" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="172" spans="1:18" x14ac:dyDescent="0.4">
@@ -8425,7 +8427,7 @@
         <v>28</v>
       </c>
       <c r="R172" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="173" spans="1:18" x14ac:dyDescent="0.4">
@@ -8457,7 +8459,7 @@
         <v>20</v>
       </c>
       <c r="R173" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" spans="1:18" x14ac:dyDescent="0.4">
@@ -8489,7 +8491,7 @@
         <v>20</v>
       </c>
       <c r="R174" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.4">
@@ -8518,7 +8520,7 @@
         <v>20</v>
       </c>
       <c r="R175" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.4">
@@ -8547,7 +8549,7 @@
         <v>20</v>
       </c>
       <c r="R176" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="177" spans="1:18" x14ac:dyDescent="0.4">
@@ -8576,7 +8578,7 @@
         <v>20</v>
       </c>
       <c r="R177" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.4">
@@ -8608,7 +8610,7 @@
         <v>20</v>
       </c>
       <c r="R178" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.4">
@@ -8637,7 +8639,7 @@
         <v>20</v>
       </c>
       <c r="R179" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="180" spans="1:18" x14ac:dyDescent="0.4">
@@ -8669,7 +8671,7 @@
         <v>74</v>
       </c>
       <c r="R180" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="181" spans="1:18" x14ac:dyDescent="0.4">
@@ -8704,7 +8706,7 @@
         <v>92</v>
       </c>
       <c r="R181" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.4">
@@ -8733,7 +8735,7 @@
         <v>20</v>
       </c>
       <c r="R182" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.4">
@@ -8771,7 +8773,7 @@
         <v>194</v>
       </c>
       <c r="R183" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.4">
@@ -8803,7 +8805,7 @@
         <v>21</v>
       </c>
       <c r="R184" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="185" spans="1:18" x14ac:dyDescent="0.4">
@@ -8832,7 +8834,7 @@
         <v>20</v>
       </c>
       <c r="R185" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.4">
@@ -8861,7 +8863,7 @@
         <v>34</v>
       </c>
       <c r="R186" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="187" spans="1:18" x14ac:dyDescent="0.4">
@@ -8890,7 +8892,7 @@
         <v>20</v>
       </c>
       <c r="R187" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="188" spans="1:18" x14ac:dyDescent="0.4">
@@ -8919,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="R188" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="189" spans="1:18" x14ac:dyDescent="0.4">
@@ -8948,7 +8950,7 @@
         <v>34</v>
       </c>
       <c r="R189" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="190" spans="1:18" x14ac:dyDescent="0.4">
@@ -8980,7 +8982,7 @@
         <v>20</v>
       </c>
       <c r="R190" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.4">
@@ -9033,7 +9035,7 @@
         <v>43</v>
       </c>
       <c r="R191" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.4">
@@ -9062,7 +9064,7 @@
         <v>20</v>
       </c>
       <c r="R192" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="193" spans="1:18" x14ac:dyDescent="0.4">
@@ -9091,7 +9093,7 @@
         <v>20</v>
       </c>
       <c r="R193" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="194" spans="1:18" x14ac:dyDescent="0.4">
@@ -9120,7 +9122,7 @@
         <v>20</v>
       </c>
       <c r="R194" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="195" spans="1:18" x14ac:dyDescent="0.4">
@@ -9152,7 +9154,7 @@
         <v>34</v>
       </c>
       <c r="R195" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.4">
@@ -9184,7 +9186,7 @@
         <v>20</v>
       </c>
       <c r="R196" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.4">
@@ -9213,7 +9215,7 @@
         <v>20</v>
       </c>
       <c r="R197" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.4">
@@ -9248,7 +9250,7 @@
         <v>42</v>
       </c>
       <c r="R198" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199" spans="1:18" x14ac:dyDescent="0.4">
@@ -9283,7 +9285,7 @@
         <v>92</v>
       </c>
       <c r="R199" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.4">
@@ -9312,7 +9314,7 @@
         <v>34</v>
       </c>
       <c r="R200" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="201" spans="1:18" x14ac:dyDescent="0.4">
@@ -9347,7 +9349,7 @@
         <v>74</v>
       </c>
       <c r="R201" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="202" spans="1:18" x14ac:dyDescent="0.4">
@@ -9408,7 +9410,7 @@
         <v>28</v>
       </c>
       <c r="R203" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.4">
@@ -9437,7 +9439,7 @@
         <v>20</v>
       </c>
       <c r="R204" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="1:18" x14ac:dyDescent="0.4">
@@ -9469,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="R205" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="206" spans="1:18" x14ac:dyDescent="0.4">
@@ -9498,7 +9500,7 @@
         <v>20</v>
       </c>
       <c r="R206" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="207" spans="1:18" x14ac:dyDescent="0.4">
@@ -9530,7 +9532,7 @@
         <v>21</v>
       </c>
       <c r="R207" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.4">
@@ -9559,7 +9561,7 @@
         <v>20</v>
       </c>
       <c r="R208" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="209" spans="1:18" x14ac:dyDescent="0.4">
@@ -9588,7 +9590,7 @@
         <v>20</v>
       </c>
       <c r="R209" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.4">
@@ -9623,7 +9625,7 @@
         <v>248</v>
       </c>
       <c r="R210" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.4">
@@ -9655,7 +9657,7 @@
         <v>42</v>
       </c>
       <c r="R211" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.4">
@@ -9690,7 +9692,7 @@
         <v>248</v>
       </c>
       <c r="R212" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="213" spans="1:18" x14ac:dyDescent="0.4">
@@ -9722,7 +9724,7 @@
         <v>20</v>
       </c>
       <c r="R213" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.4">
@@ -9751,7 +9753,7 @@
         <v>20</v>
       </c>
       <c r="R214" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.4">
@@ -9783,7 +9785,7 @@
         <v>20</v>
       </c>
       <c r="R215" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="216" spans="1:18" x14ac:dyDescent="0.4">
@@ -9812,7 +9814,7 @@
         <v>20</v>
       </c>
       <c r="R216" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="217" spans="1:18" x14ac:dyDescent="0.4">
@@ -9841,7 +9843,7 @@
         <v>20</v>
       </c>
       <c r="R217" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.4">
@@ -9873,7 +9875,7 @@
         <v>20</v>
       </c>
       <c r="R218" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="219" spans="1:18" x14ac:dyDescent="0.4">
@@ -9905,7 +9907,7 @@
         <v>34</v>
       </c>
       <c r="R219" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="220" spans="1:18" x14ac:dyDescent="0.4">
@@ -9940,7 +9942,7 @@
         <v>248</v>
       </c>
       <c r="R220" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="221" spans="1:18" x14ac:dyDescent="0.4">
@@ -9978,7 +9980,7 @@
         <v>248</v>
       </c>
       <c r="R221" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="222" spans="1:18" x14ac:dyDescent="0.4">
@@ -10013,7 +10015,7 @@
         <v>44</v>
       </c>
       <c r="R222" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.4">
@@ -10045,7 +10047,7 @@
         <v>20</v>
       </c>
       <c r="R223" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="224" spans="1:18" x14ac:dyDescent="0.4">
@@ -10074,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="R224" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="225" spans="1:18" x14ac:dyDescent="0.4">
@@ -10103,7 +10105,7 @@
         <v>20</v>
       </c>
       <c r="R225" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="226" spans="1:18" x14ac:dyDescent="0.4">
@@ -10132,7 +10134,7 @@
         <v>77</v>
       </c>
       <c r="R226" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="227" spans="1:18" x14ac:dyDescent="0.4">
@@ -10161,7 +10163,7 @@
         <v>20</v>
       </c>
       <c r="R227" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.4">
@@ -10190,7 +10192,7 @@
         <v>77</v>
       </c>
       <c r="R228" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="229" spans="1:18" x14ac:dyDescent="0.4">
@@ -10219,7 +10221,7 @@
         <v>77</v>
       </c>
       <c r="R229" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="230" spans="1:18" x14ac:dyDescent="0.4">
@@ -10248,7 +10250,7 @@
         <v>20</v>
       </c>
       <c r="R230" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.4">
@@ -10277,7 +10279,7 @@
         <v>77</v>
       </c>
       <c r="R231" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="232" spans="1:18" x14ac:dyDescent="0.4">
@@ -10306,7 +10308,7 @@
         <v>34</v>
       </c>
       <c r="R232" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="233" spans="1:18" x14ac:dyDescent="0.4">
@@ -10335,7 +10337,7 @@
         <v>77</v>
       </c>
       <c r="R233" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="234" spans="1:18" x14ac:dyDescent="0.4">
@@ -10364,7 +10366,7 @@
         <v>165</v>
       </c>
       <c r="R234" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="235" spans="1:18" x14ac:dyDescent="0.4">
@@ -10396,7 +10398,7 @@
         <v>165</v>
       </c>
       <c r="R235" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="236" spans="1:18" x14ac:dyDescent="0.4">
@@ -10425,7 +10427,7 @@
         <v>20</v>
       </c>
       <c r="R236" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="237" spans="1:18" x14ac:dyDescent="0.4">
@@ -10454,7 +10456,7 @@
         <v>20</v>
       </c>
       <c r="R237" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="238" spans="1:18" x14ac:dyDescent="0.4">
@@ -10483,7 +10485,7 @@
         <v>20</v>
       </c>
       <c r="R238" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="239" spans="1:18" x14ac:dyDescent="0.4">
@@ -10512,7 +10514,7 @@
         <v>20</v>
       </c>
       <c r="R239" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="240" spans="1:18" x14ac:dyDescent="0.4">
@@ -10547,7 +10549,7 @@
         <v>43</v>
       </c>
       <c r="R240" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="241" spans="1:18" x14ac:dyDescent="0.4">
@@ -10576,7 +10578,7 @@
         <v>20</v>
       </c>
       <c r="R241" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="242" spans="1:18" x14ac:dyDescent="0.4">
@@ -10605,7 +10607,7 @@
         <v>20</v>
       </c>
       <c r="R242" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.4">
@@ -10634,7 +10636,7 @@
         <v>20</v>
       </c>
       <c r="R243" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="244" spans="1:18" x14ac:dyDescent="0.4">
@@ -10663,7 +10665,7 @@
         <v>34</v>
       </c>
       <c r="R244" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="245" spans="1:18" x14ac:dyDescent="0.4">
@@ -10692,7 +10694,7 @@
         <v>20</v>
       </c>
       <c r="R245" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="246" spans="1:18" x14ac:dyDescent="0.4">
@@ -10721,7 +10723,7 @@
         <v>20</v>
       </c>
       <c r="R246" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="247" spans="1:18" x14ac:dyDescent="0.4">
@@ -10753,7 +10755,7 @@
         <v>34</v>
       </c>
       <c r="R247" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="248" spans="1:18" x14ac:dyDescent="0.4">
@@ -10791,7 +10793,7 @@
         <v>28</v>
       </c>
       <c r="R248" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="249" spans="1:18" x14ac:dyDescent="0.4">
@@ -10829,7 +10831,7 @@
         <v>28</v>
       </c>
       <c r="R249" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="250" spans="1:18" x14ac:dyDescent="0.4">
@@ -10861,7 +10863,7 @@
         <v>20</v>
       </c>
       <c r="R250" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="251" spans="1:18" x14ac:dyDescent="0.4">
@@ -10893,7 +10895,7 @@
         <v>20</v>
       </c>
       <c r="R251" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="252" spans="1:18" x14ac:dyDescent="0.4">
@@ -10928,7 +10930,7 @@
         <v>75</v>
       </c>
       <c r="R252" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="253" spans="1:18" x14ac:dyDescent="0.4">
@@ -10957,7 +10959,7 @@
         <v>20</v>
       </c>
       <c r="R253" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="254" spans="1:18" x14ac:dyDescent="0.4">
@@ -10986,7 +10988,7 @@
         <v>34</v>
       </c>
       <c r="R254" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="255" spans="1:18" x14ac:dyDescent="0.4">
@@ -11015,7 +11017,7 @@
         <v>20</v>
       </c>
       <c r="R255" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="256" spans="1:18" x14ac:dyDescent="0.4">
@@ -11044,7 +11046,7 @@
         <v>20</v>
       </c>
       <c r="R256" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="257" spans="1:18" x14ac:dyDescent="0.4">
@@ -11073,7 +11075,7 @@
         <v>20</v>
       </c>
       <c r="R257" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="258" spans="1:18" x14ac:dyDescent="0.4">
@@ -11102,7 +11104,7 @@
         <v>20</v>
       </c>
       <c r="R258" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.4">
@@ -11131,7 +11133,7 @@
         <v>34</v>
       </c>
       <c r="R259" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="260" spans="1:18" x14ac:dyDescent="0.4">
@@ -11160,7 +11162,7 @@
         <v>20</v>
       </c>
       <c r="R260" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.4">
@@ -11192,7 +11194,7 @@
         <v>43</v>
       </c>
       <c r="R261" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.4">
@@ -11224,7 +11226,7 @@
         <v>42</v>
       </c>
       <c r="R262" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.4">
@@ -11259,7 +11261,7 @@
         <v>378</v>
       </c>
       <c r="R263" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.4">
@@ -11303,7 +11305,7 @@
         <v>28</v>
       </c>
       <c r="R264" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.4">
@@ -11350,7 +11352,7 @@
         <v>28</v>
       </c>
       <c r="R265" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.4">
@@ -11394,7 +11396,7 @@
         <v>28</v>
       </c>
       <c r="R266" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.4">
@@ -11426,7 +11428,7 @@
         <v>20</v>
       </c>
       <c r="R267" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.4">
@@ -11458,7 +11460,7 @@
         <v>34</v>
       </c>
       <c r="R268" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.4">
@@ -11490,7 +11492,7 @@
         <v>20</v>
       </c>
       <c r="R269" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.4">
@@ -11522,7 +11524,7 @@
         <v>20</v>
       </c>
       <c r="R270" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.4">
@@ -11554,7 +11556,7 @@
         <v>20</v>
       </c>
       <c r="R271" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.4">
@@ -11586,7 +11588,7 @@
         <v>20</v>
       </c>
       <c r="R272" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.4">
@@ -11618,7 +11620,7 @@
         <v>20</v>
       </c>
       <c r="R273" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="274" spans="1:18" x14ac:dyDescent="0.4">
@@ -11659,7 +11661,7 @@
         <v>74</v>
       </c>
       <c r="R274" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="275" spans="1:18" x14ac:dyDescent="0.4">
@@ -11691,7 +11693,7 @@
         <v>20</v>
       </c>
       <c r="R275" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.4">
@@ -11723,7 +11725,7 @@
         <v>20</v>
       </c>
       <c r="R276" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.4">
@@ -11764,7 +11766,7 @@
         <v>28</v>
       </c>
       <c r="R277" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="278" spans="1:18" x14ac:dyDescent="0.4">
@@ -11793,7 +11795,7 @@
         <v>20</v>
       </c>
       <c r="R278" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="279" spans="1:18" x14ac:dyDescent="0.4">
@@ -11825,7 +11827,7 @@
         <v>20</v>
       </c>
       <c r="R279" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="280" spans="1:18" x14ac:dyDescent="0.4">
@@ -11860,7 +11862,7 @@
         <v>42</v>
       </c>
       <c r="R280" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="281" spans="1:18" x14ac:dyDescent="0.4">
@@ -11892,7 +11894,7 @@
         <v>20</v>
       </c>
       <c r="R281" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="282" spans="1:18" x14ac:dyDescent="0.4">
@@ -11933,7 +11935,7 @@
         <v>92</v>
       </c>
       <c r="R282" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="283" spans="1:18" x14ac:dyDescent="0.4">
@@ -11968,7 +11970,7 @@
         <v>28</v>
       </c>
       <c r="R283" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="284" spans="1:18" x14ac:dyDescent="0.4">
@@ -12000,7 +12002,7 @@
         <v>20</v>
       </c>
       <c r="R284" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="285" spans="1:18" x14ac:dyDescent="0.4">
@@ -12029,7 +12031,7 @@
         <v>20</v>
       </c>
       <c r="R285" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.4">
@@ -12058,7 +12060,7 @@
         <v>20</v>
       </c>
       <c r="R286" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="287" spans="1:18" x14ac:dyDescent="0.4">
@@ -12090,7 +12092,7 @@
         <v>21</v>
       </c>
       <c r="R287" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="288" spans="1:18" x14ac:dyDescent="0.4">
@@ -12145,7 +12147,7 @@
         <v>20</v>
       </c>
       <c r="R289" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.4">
@@ -12174,7 +12176,7 @@
         <v>34</v>
       </c>
       <c r="R290" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.4">
@@ -12206,7 +12208,7 @@
         <v>248</v>
       </c>
       <c r="R291" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.4">
@@ -12235,7 +12237,7 @@
         <v>20</v>
       </c>
       <c r="R292" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.4">
@@ -12267,7 +12269,7 @@
         <v>378</v>
       </c>
       <c r="R293" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.4">
@@ -12299,7 +12301,7 @@
         <v>378</v>
       </c>
       <c r="R294" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="295" spans="1:18" x14ac:dyDescent="0.4">
@@ -12331,7 +12333,7 @@
         <v>77</v>
       </c>
       <c r="R295" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.4">
@@ -12360,7 +12362,7 @@
         <v>20</v>
       </c>
       <c r="R296" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.4">
@@ -12395,7 +12397,7 @@
         <v>75</v>
       </c>
       <c r="R297" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.4">
@@ -12436,7 +12438,7 @@
         <v>248</v>
       </c>
       <c r="R298" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.4">
@@ -12477,7 +12479,7 @@
         <v>248</v>
       </c>
       <c r="R299" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.4">
@@ -12509,7 +12511,7 @@
         <v>34</v>
       </c>
       <c r="R300" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.4">
@@ -12538,7 +12540,7 @@
         <v>20</v>
       </c>
       <c r="R301" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.4">
@@ -12567,7 +12569,7 @@
         <v>20</v>
       </c>
       <c r="R302" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.4">
@@ -12605,7 +12607,7 @@
         <v>44</v>
       </c>
       <c r="R303" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.4">
@@ -12643,7 +12645,7 @@
         <v>92</v>
       </c>
       <c r="R304" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.4">
@@ -12678,7 +12680,7 @@
         <v>194</v>
       </c>
       <c r="R305" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.4">
@@ -12716,7 +12718,7 @@
         <v>43</v>
       </c>
       <c r="R306" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.4">
@@ -12751,7 +12753,7 @@
         <v>43</v>
       </c>
       <c r="R307" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.4">
@@ -12786,7 +12788,7 @@
         <v>42</v>
       </c>
       <c r="R308" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.4">
@@ -12818,7 +12820,7 @@
         <v>20</v>
       </c>
       <c r="R309" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.4">
@@ -12847,7 +12849,7 @@
         <v>20</v>
       </c>
       <c r="R310" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.4">
@@ -12879,7 +12881,7 @@
         <v>20</v>
       </c>
       <c r="R311" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.4">
@@ -12911,7 +12913,7 @@
         <v>20</v>
       </c>
       <c r="R312" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.4">
@@ -12952,7 +12954,7 @@
         <v>28</v>
       </c>
       <c r="R313" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.4">
@@ -12981,7 +12983,7 @@
         <v>20</v>
       </c>
       <c r="R314" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.4">
@@ -13010,7 +13012,7 @@
         <v>20</v>
       </c>
       <c r="R315" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.4">
@@ -13039,7 +13041,7 @@
         <v>20</v>
       </c>
       <c r="R316" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.4">
@@ -13077,7 +13079,7 @@
         <v>28</v>
       </c>
       <c r="R317" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.4">
@@ -13106,7 +13108,7 @@
         <v>20</v>
       </c>
       <c r="R318" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.4">
@@ -13144,7 +13146,7 @@
         <v>92</v>
       </c>
       <c r="R319" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.4">
@@ -13173,7 +13175,7 @@
         <v>20</v>
       </c>
       <c r="R320" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.4">
@@ -13208,7 +13210,7 @@
         <v>29</v>
       </c>
       <c r="R321" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.4">
@@ -13237,7 +13239,7 @@
         <v>34</v>
       </c>
       <c r="R322" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.4">
@@ -13266,7 +13268,7 @@
         <v>20</v>
       </c>
       <c r="R323" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.4">
@@ -13295,7 +13297,7 @@
         <v>20</v>
       </c>
       <c r="R324" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.4">
@@ -13324,7 +13326,7 @@
         <v>20</v>
       </c>
       <c r="R325" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.4">
@@ -13356,7 +13358,7 @@
         <v>44</v>
       </c>
       <c r="R326" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.4">
@@ -13388,7 +13390,7 @@
         <v>75</v>
       </c>
       <c r="R327" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.4">
@@ -13417,7 +13419,7 @@
         <v>20</v>
       </c>
       <c r="R328" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.4">
@@ -13446,7 +13448,7 @@
         <v>20</v>
       </c>
       <c r="R329" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.4">
@@ -13475,7 +13477,7 @@
         <v>20</v>
       </c>
       <c r="R330" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.4">
@@ -13504,7 +13506,7 @@
         <v>20</v>
       </c>
       <c r="R331" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.4">
@@ -13512,7 +13514,7 @@
         <v>913</v>
       </c>
       <c r="B332" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C332">
         <v>742</v>
@@ -13574,7 +13576,7 @@
         <v>20</v>
       </c>
       <c r="R333" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.4">
@@ -13606,7 +13608,7 @@
         <v>20</v>
       </c>
       <c r="R334" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.4">
@@ -13641,7 +13643,7 @@
         <v>42</v>
       </c>
       <c r="R335" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.4">
@@ -13676,7 +13678,7 @@
         <v>21</v>
       </c>
       <c r="R336" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.4">
@@ -13708,7 +13710,7 @@
         <v>92</v>
       </c>
       <c r="R337" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.4">
@@ -13737,7 +13739,7 @@
         <v>20</v>
       </c>
       <c r="R338" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.4">
@@ -13766,7 +13768,7 @@
         <v>34</v>
       </c>
       <c r="R339" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.4">
@@ -13795,7 +13797,7 @@
         <v>20</v>
       </c>
       <c r="R340" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.4">
@@ -13824,7 +13826,7 @@
         <v>34</v>
       </c>
       <c r="R341" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.4">
@@ -13853,7 +13855,7 @@
         <v>34</v>
       </c>
       <c r="R342" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.4">
@@ -13882,7 +13884,7 @@
         <v>20</v>
       </c>
       <c r="R343" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.4">
@@ -13911,7 +13913,7 @@
         <v>20</v>
       </c>
       <c r="R344" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.4">
@@ -13940,7 +13942,7 @@
         <v>20</v>
       </c>
       <c r="R345" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.4">
@@ -13969,7 +13971,7 @@
         <v>20</v>
       </c>
       <c r="R346" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.4">
@@ -13998,7 +14000,7 @@
         <v>20</v>
       </c>
       <c r="R347" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.4">
@@ -14027,7 +14029,7 @@
         <v>20</v>
       </c>
       <c r="R348" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.4">
@@ -14056,7 +14058,7 @@
         <v>20</v>
       </c>
       <c r="R349" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.4">
@@ -14085,7 +14087,7 @@
         <v>20</v>
       </c>
       <c r="R350" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.4">
@@ -14114,7 +14116,7 @@
         <v>20</v>
       </c>
       <c r="R351" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.4">
@@ -14146,7 +14148,7 @@
         <v>20</v>
       </c>
       <c r="R352" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.4">
@@ -14193,7 +14195,7 @@
         <v>248</v>
       </c>
       <c r="R353" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.4">
@@ -14222,7 +14224,7 @@
         <v>20</v>
       </c>
       <c r="R354" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.4">
@@ -14266,7 +14268,7 @@
         <v>44</v>
       </c>
       <c r="R355" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.4">
@@ -14307,7 +14309,7 @@
         <v>43</v>
       </c>
       <c r="R356" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.4">
@@ -14345,7 +14347,7 @@
         <v>92</v>
       </c>
       <c r="R357" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.4">
@@ -14395,7 +14397,7 @@
         <v>248</v>
       </c>
       <c r="R358" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.4">
@@ -14430,7 +14432,7 @@
         <v>92</v>
       </c>
       <c r="R359" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.4">
@@ -14474,7 +14476,7 @@
         <v>248</v>
       </c>
       <c r="R360" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.4">
@@ -14515,7 +14517,7 @@
         <v>92</v>
       </c>
       <c r="R361" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.4">
@@ -14571,7 +14573,7 @@
         <v>74</v>
       </c>
       <c r="R362" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.4">
@@ -14615,7 +14617,7 @@
         <v>248</v>
       </c>
       <c r="R363" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.4">
@@ -14659,7 +14661,7 @@
         <v>248</v>
       </c>
       <c r="R364" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.4">
@@ -14691,7 +14693,7 @@
         <v>20</v>
       </c>
       <c r="R365" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.4">
@@ -14735,7 +14737,7 @@
         <v>43</v>
       </c>
       <c r="R366" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.4">
@@ -14782,7 +14784,7 @@
         <v>43</v>
       </c>
       <c r="R367" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.4">
@@ -14814,7 +14816,7 @@
         <v>34</v>
       </c>
       <c r="R368" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="369" spans="1:18" x14ac:dyDescent="0.4">
@@ -14858,7 +14860,7 @@
         <v>248</v>
       </c>
       <c r="R369" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.4">
@@ -14905,7 +14907,7 @@
         <v>248</v>
       </c>
       <c r="R370" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="371" spans="1:18" x14ac:dyDescent="0.4">
@@ -14934,7 +14936,7 @@
         <v>77</v>
       </c>
       <c r="R371" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="372" spans="1:18" x14ac:dyDescent="0.4">
@@ -14963,7 +14965,7 @@
         <v>77</v>
       </c>
       <c r="R372" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="373" spans="1:18" x14ac:dyDescent="0.4">
@@ -14992,7 +14994,7 @@
         <v>77</v>
       </c>
       <c r="R373" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.4">
@@ -15021,7 +15023,7 @@
         <v>20</v>
       </c>
       <c r="R374" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.4">
@@ -15050,7 +15052,7 @@
         <v>20</v>
       </c>
       <c r="R375" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="376" spans="1:18" x14ac:dyDescent="0.4">
@@ -15094,7 +15096,7 @@
         <v>248</v>
       </c>
       <c r="R376" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="377" spans="1:18" x14ac:dyDescent="0.4">
@@ -15138,7 +15140,7 @@
         <v>248</v>
       </c>
       <c r="R377" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="378" spans="1:18" x14ac:dyDescent="0.4">
@@ -15182,7 +15184,7 @@
         <v>248</v>
       </c>
       <c r="R378" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="379" spans="1:18" x14ac:dyDescent="0.4">
@@ -15211,7 +15213,7 @@
         <v>34</v>
       </c>
       <c r="R379" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="380" spans="1:18" x14ac:dyDescent="0.4">
@@ -15243,7 +15245,7 @@
         <v>34</v>
       </c>
       <c r="R380" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="381" spans="1:18" x14ac:dyDescent="0.4">
@@ -15275,7 +15277,7 @@
         <v>20</v>
       </c>
       <c r="R381" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="382" spans="1:18" x14ac:dyDescent="0.4">
@@ -15307,7 +15309,7 @@
         <v>20</v>
       </c>
       <c r="R382" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="383" spans="1:18" x14ac:dyDescent="0.4">
@@ -15354,7 +15356,7 @@
         <v>248</v>
       </c>
       <c r="R383" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="384" spans="1:18" x14ac:dyDescent="0.4">
@@ -15389,7 +15391,7 @@
         <v>43</v>
       </c>
       <c r="R384" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="385" spans="1:18" x14ac:dyDescent="0.4">
@@ -15421,7 +15423,7 @@
         <v>20</v>
       </c>
       <c r="R385" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="386" spans="1:18" x14ac:dyDescent="0.4">
@@ -15450,7 +15452,7 @@
         <v>165</v>
       </c>
       <c r="R386" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="387" spans="1:18" x14ac:dyDescent="0.4">
@@ -15479,7 +15481,7 @@
         <v>34</v>
       </c>
       <c r="R387" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="388" spans="1:18" x14ac:dyDescent="0.4">
@@ -15508,7 +15510,7 @@
         <v>20</v>
       </c>
       <c r="R388" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="389" spans="1:18" x14ac:dyDescent="0.4">
@@ -15537,7 +15539,7 @@
         <v>20</v>
       </c>
       <c r="R389" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="390" spans="1:18" x14ac:dyDescent="0.4">
@@ -15569,7 +15571,7 @@
         <v>34</v>
       </c>
       <c r="R390" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="391" spans="1:18" x14ac:dyDescent="0.4">
@@ -15604,7 +15606,7 @@
         <v>74</v>
       </c>
       <c r="R391" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="392" spans="1:18" x14ac:dyDescent="0.4">
@@ -15639,7 +15641,7 @@
         <v>86</v>
       </c>
       <c r="R392" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="393" spans="1:18" x14ac:dyDescent="0.4">
@@ -15674,7 +15676,7 @@
         <v>42</v>
       </c>
       <c r="R393" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="394" spans="1:18" x14ac:dyDescent="0.4">
@@ -15706,7 +15708,7 @@
         <v>21</v>
       </c>
       <c r="R394" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="395" spans="1:18" x14ac:dyDescent="0.4">
@@ -15735,7 +15737,7 @@
         <v>34</v>
       </c>
       <c r="R395" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="396" spans="1:18" x14ac:dyDescent="0.4">
@@ -15767,7 +15769,7 @@
         <v>20</v>
       </c>
       <c r="R396" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="397" spans="1:18" x14ac:dyDescent="0.4">
@@ -15796,7 +15798,7 @@
         <v>34</v>
       </c>
       <c r="R397" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="398" spans="1:18" x14ac:dyDescent="0.4">
@@ -15828,7 +15830,7 @@
         <v>20</v>
       </c>
       <c r="R398" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="399" spans="1:18" x14ac:dyDescent="0.4">
@@ -15857,7 +15859,7 @@
         <v>20</v>
       </c>
       <c r="R399" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="400" spans="1:18" x14ac:dyDescent="0.4">
@@ -15886,7 +15888,7 @@
         <v>20</v>
       </c>
       <c r="R400" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="401" spans="1:18" x14ac:dyDescent="0.4">
@@ -15915,7 +15917,7 @@
         <v>34</v>
       </c>
       <c r="R401" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="402" spans="1:18" x14ac:dyDescent="0.4">
@@ -15944,7 +15946,7 @@
         <v>20</v>
       </c>
       <c r="R402" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="403" spans="1:18" x14ac:dyDescent="0.4">
@@ -15988,7 +15990,7 @@
         <v>22</v>
       </c>
       <c r="R403" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="404" spans="1:18" x14ac:dyDescent="0.4">
@@ -16017,7 +16019,7 @@
         <v>20</v>
       </c>
       <c r="R404" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="405" spans="1:18" x14ac:dyDescent="0.4">
@@ -16046,7 +16048,7 @@
         <v>20</v>
       </c>
       <c r="R405" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="406" spans="1:18" x14ac:dyDescent="0.4">
@@ -16081,7 +16083,7 @@
         <v>44</v>
       </c>
       <c r="R406" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="407" spans="1:18" x14ac:dyDescent="0.4">
@@ -16110,7 +16112,7 @@
         <v>20</v>
       </c>
       <c r="R407" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="408" spans="1:18" x14ac:dyDescent="0.4">
@@ -16139,7 +16141,7 @@
         <v>20</v>
       </c>
       <c r="R408" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="409" spans="1:18" x14ac:dyDescent="0.4">
@@ -16168,7 +16170,7 @@
         <v>20</v>
       </c>
       <c r="R409" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="410" spans="1:18" x14ac:dyDescent="0.4">
@@ -16197,7 +16199,7 @@
         <v>20</v>
       </c>
       <c r="R410" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="411" spans="1:18" x14ac:dyDescent="0.4">
@@ -16226,7 +16228,7 @@
         <v>20</v>
       </c>
       <c r="R411" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="412" spans="1:18" x14ac:dyDescent="0.4">
@@ -16255,7 +16257,7 @@
         <v>34</v>
       </c>
       <c r="R412" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="413" spans="1:18" x14ac:dyDescent="0.4">
@@ -16284,7 +16286,7 @@
         <v>20</v>
       </c>
       <c r="R413" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="414" spans="1:18" x14ac:dyDescent="0.4">
@@ -16313,7 +16315,7 @@
         <v>34</v>
       </c>
       <c r="R414" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="415" spans="1:18" x14ac:dyDescent="0.4">
@@ -16342,7 +16344,7 @@
         <v>20</v>
       </c>
       <c r="R415" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="416" spans="1:18" x14ac:dyDescent="0.4">
@@ -16371,7 +16373,7 @@
         <v>20</v>
       </c>
       <c r="R416" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="417" spans="1:18" x14ac:dyDescent="0.4">
@@ -16403,7 +16405,7 @@
         <v>248</v>
       </c>
       <c r="R417" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="418" spans="1:18" x14ac:dyDescent="0.4">
@@ -16435,7 +16437,7 @@
         <v>20</v>
       </c>
       <c r="R418" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="419" spans="1:18" x14ac:dyDescent="0.4">
@@ -16464,7 +16466,7 @@
         <v>20</v>
       </c>
       <c r="R419" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="420" spans="1:18" x14ac:dyDescent="0.4">
@@ -16496,7 +16498,7 @@
         <v>20</v>
       </c>
       <c r="R420" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="421" spans="1:18" x14ac:dyDescent="0.4">
@@ -16531,7 +16533,7 @@
         <v>194</v>
       </c>
       <c r="R421" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="422" spans="1:18" x14ac:dyDescent="0.4">
@@ -16575,7 +16577,7 @@
         <v>92</v>
       </c>
       <c r="R422" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="423" spans="1:18" x14ac:dyDescent="0.4">
@@ -16604,7 +16606,7 @@
         <v>34</v>
       </c>
       <c r="R423" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="424" spans="1:18" x14ac:dyDescent="0.4">
@@ -16612,7 +16614,7 @@
         <v>1512</v>
       </c>
       <c r="B424" t="s">
-        <v>567</v>
+        <v>612</v>
       </c>
       <c r="C424">
         <v>965</v>
@@ -16633,7 +16635,7 @@
         <v>34</v>
       </c>
       <c r="R424" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="425" spans="1:18" x14ac:dyDescent="0.4">
@@ -16641,7 +16643,7 @@
         <v>1513</v>
       </c>
       <c r="B425" t="s">
-        <v>568</v>
+        <v>610</v>
       </c>
       <c r="C425">
         <v>965</v>
@@ -16662,7 +16664,7 @@
         <v>20</v>
       </c>
       <c r="R425" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="426" spans="1:18" x14ac:dyDescent="0.4">
@@ -16670,7 +16672,7 @@
         <v>1513</v>
       </c>
       <c r="B426" t="s">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="C426">
         <v>965</v>
@@ -16691,7 +16693,7 @@
         <v>20</v>
       </c>
       <c r="R426" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="427" spans="1:18" x14ac:dyDescent="0.4">
@@ -16699,7 +16701,7 @@
         <v>1551</v>
       </c>
       <c r="B427" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C427">
         <v>978</v>
@@ -16726,7 +16728,7 @@
         <v>43</v>
       </c>
       <c r="R427" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="428" spans="1:18" x14ac:dyDescent="0.4">
@@ -16734,7 +16736,7 @@
         <v>1552</v>
       </c>
       <c r="B428" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C428">
         <v>978</v>
@@ -16755,7 +16757,7 @@
         <v>20</v>
       </c>
       <c r="R428" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="429" spans="1:18" x14ac:dyDescent="0.4">
@@ -16763,7 +16765,7 @@
         <v>1553</v>
       </c>
       <c r="B429" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C429">
         <v>978</v>
@@ -16784,7 +16786,7 @@
         <v>34</v>
       </c>
       <c r="R429" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="430" spans="1:18" x14ac:dyDescent="0.4">
@@ -16792,7 +16794,7 @@
         <v>1554</v>
       </c>
       <c r="B430" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C430">
         <v>978</v>
@@ -16813,7 +16815,7 @@
         <v>20</v>
       </c>
       <c r="R430" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="431" spans="1:18" x14ac:dyDescent="0.4">
@@ -16821,7 +16823,7 @@
         <v>1568</v>
       </c>
       <c r="B431" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C431">
         <v>981</v>
@@ -16842,7 +16844,7 @@
         <v>20</v>
       </c>
       <c r="R431" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="432" spans="1:18" x14ac:dyDescent="0.4">
@@ -16850,7 +16852,7 @@
         <v>1578</v>
       </c>
       <c r="B432" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C432">
         <v>984</v>
@@ -16874,7 +16876,7 @@
         <v>21</v>
       </c>
       <c r="R432" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="433" spans="1:18" x14ac:dyDescent="0.4">
@@ -16882,7 +16884,7 @@
         <v>1624</v>
       </c>
       <c r="B433" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C433">
         <v>1011</v>
@@ -16900,13 +16902,13 @@
         <v>287</v>
       </c>
       <c r="H433" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I433" t="s">
         <v>77</v>
       </c>
       <c r="R433" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="434" spans="1:18" x14ac:dyDescent="0.4">
@@ -16914,7 +16916,7 @@
         <v>1635</v>
       </c>
       <c r="B434" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C434">
         <v>1024</v>
@@ -16932,13 +16934,13 @@
         <v>287</v>
       </c>
       <c r="H434" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I434" t="s">
         <v>20</v>
       </c>
       <c r="R434" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="435" spans="1:18" x14ac:dyDescent="0.4">
@@ -16946,7 +16948,7 @@
         <v>1636</v>
       </c>
       <c r="B435" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C435">
         <v>1024</v>
@@ -16964,13 +16966,13 @@
         <v>287</v>
       </c>
       <c r="H435" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="I435" t="s">
         <v>20</v>
       </c>
       <c r="R435" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="436" spans="1:18" x14ac:dyDescent="0.4">
@@ -16978,7 +16980,7 @@
         <v>1641</v>
       </c>
       <c r="B436" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C436">
         <v>1030</v>
@@ -16999,7 +17001,7 @@
         <v>20</v>
       </c>
       <c r="R436" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="437" spans="1:18" x14ac:dyDescent="0.4">
@@ -17007,7 +17009,7 @@
         <v>1678</v>
       </c>
       <c r="B437" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C437">
         <v>1053</v>
@@ -17028,7 +17030,7 @@
         <v>20</v>
       </c>
       <c r="R437" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="438" spans="1:18" x14ac:dyDescent="0.4">
@@ -17036,7 +17038,7 @@
         <v>1695</v>
       </c>
       <c r="B438" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C438">
         <v>1059</v>
@@ -17054,13 +17056,13 @@
         <v>46</v>
       </c>
       <c r="H438" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I438" t="s">
         <v>34</v>
       </c>
       <c r="R438" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="439" spans="1:18" x14ac:dyDescent="0.4">
@@ -17068,7 +17070,7 @@
         <v>1696</v>
       </c>
       <c r="B439" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C439">
         <v>1059</v>
@@ -17086,13 +17088,13 @@
         <v>46</v>
       </c>
       <c r="H439" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I439" t="s">
         <v>20</v>
       </c>
       <c r="R439" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="440" spans="1:18" x14ac:dyDescent="0.4">
@@ -17100,7 +17102,7 @@
         <v>1702</v>
       </c>
       <c r="B440" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C440">
         <v>1061</v>
@@ -17121,7 +17123,7 @@
         <v>34</v>
       </c>
       <c r="R440" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="441" spans="1:18" x14ac:dyDescent="0.4">
@@ -17129,7 +17131,7 @@
         <v>1703</v>
       </c>
       <c r="B441" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C441">
         <v>1061</v>
@@ -17150,7 +17152,7 @@
         <v>20</v>
       </c>
       <c r="R441" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="442" spans="1:18" x14ac:dyDescent="0.4">
@@ -17158,7 +17160,7 @@
         <v>1704</v>
       </c>
       <c r="B442" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C442">
         <v>1061</v>
@@ -17176,13 +17178,13 @@
         <v>46</v>
       </c>
       <c r="H442" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I442" t="s">
         <v>34</v>
       </c>
       <c r="R442" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="443" spans="1:18" x14ac:dyDescent="0.4">
@@ -17190,7 +17192,7 @@
         <v>1713</v>
       </c>
       <c r="B443" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C443">
         <v>1062</v>
@@ -17208,13 +17210,13 @@
         <v>46</v>
       </c>
       <c r="H443" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I443" t="s">
         <v>20</v>
       </c>
       <c r="R443" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="444" spans="1:18" x14ac:dyDescent="0.4">
@@ -17222,7 +17224,7 @@
         <v>1717</v>
       </c>
       <c r="B444" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C444">
         <v>1062</v>
@@ -17240,13 +17242,13 @@
         <v>46</v>
       </c>
       <c r="H444" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I444" t="s">
         <v>34</v>
       </c>
       <c r="R444" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="445" spans="1:18" x14ac:dyDescent="0.4">
@@ -17254,7 +17256,7 @@
         <v>1718</v>
       </c>
       <c r="B445" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C445">
         <v>1062</v>
@@ -17272,13 +17274,13 @@
         <v>46</v>
       </c>
       <c r="H445" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I445" t="s">
         <v>20</v>
       </c>
       <c r="R445" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="446" spans="1:18" x14ac:dyDescent="0.4">
@@ -17286,7 +17288,7 @@
         <v>1737</v>
       </c>
       <c r="B446" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C446">
         <v>1065</v>
@@ -17304,13 +17306,13 @@
         <v>46</v>
       </c>
       <c r="H446" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I446" t="s">
         <v>20</v>
       </c>
       <c r="R446" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="447" spans="1:18" x14ac:dyDescent="0.4">
@@ -17318,7 +17320,7 @@
         <v>1738</v>
       </c>
       <c r="B447" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C447">
         <v>1065</v>
@@ -17336,13 +17338,13 @@
         <v>46</v>
       </c>
       <c r="H447" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I447" t="s">
         <v>20</v>
       </c>
       <c r="R447" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="448" spans="1:18" x14ac:dyDescent="0.4">
@@ -17350,7 +17352,7 @@
         <v>1739</v>
       </c>
       <c r="B448" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C448">
         <v>1065</v>
@@ -17368,13 +17370,13 @@
         <v>46</v>
       </c>
       <c r="H448" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I448" t="s">
         <v>20</v>
       </c>
       <c r="R448" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="449" spans="1:18" x14ac:dyDescent="0.4">
@@ -17382,7 +17384,7 @@
         <v>1740</v>
       </c>
       <c r="B449" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C449">
         <v>1065</v>
@@ -17400,13 +17402,13 @@
         <v>46</v>
       </c>
       <c r="H449" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I449" t="s">
         <v>34</v>
       </c>
       <c r="R449" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="450" spans="1:18" x14ac:dyDescent="0.4">
@@ -17414,7 +17416,7 @@
         <v>1742</v>
       </c>
       <c r="B450" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C450">
         <v>1066</v>
@@ -17432,13 +17434,13 @@
         <v>98</v>
       </c>
       <c r="H450" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="I450" t="s">
         <v>20</v>
       </c>
       <c r="R450" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="451" spans="1:18" x14ac:dyDescent="0.4">
@@ -17446,7 +17448,7 @@
         <v>1771</v>
       </c>
       <c r="B451" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C451">
         <v>1080</v>
@@ -17473,7 +17475,7 @@
         <v>29</v>
       </c>
       <c r="R451" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="452" spans="1:18" x14ac:dyDescent="0.4">
@@ -17481,7 +17483,7 @@
         <v>1792</v>
       </c>
       <c r="B452" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C452">
         <v>1095</v>
@@ -17499,7 +17501,7 @@
         <v>46</v>
       </c>
       <c r="H452" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="I452" t="s">
         <v>34</v>
@@ -17508,7 +17510,7 @@
         <v>92</v>
       </c>
       <c r="R452" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="453" spans="1:18" x14ac:dyDescent="0.4">
@@ -17516,7 +17518,7 @@
         <v>1818</v>
       </c>
       <c r="B453" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C453">
         <v>1099</v>
@@ -17543,7 +17545,7 @@
         <v>74</v>
       </c>
       <c r="R453" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="454" spans="1:18" x14ac:dyDescent="0.4">
@@ -17551,7 +17553,7 @@
         <v>1821</v>
       </c>
       <c r="B454" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C454">
         <v>1110</v>
@@ -17577,7 +17579,7 @@
         <v>1822</v>
       </c>
       <c r="B455" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C455">
         <v>1154</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22DADCD-AECE-4BB4-BACE-1DCC41F23880}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EAB7C5B-D10D-434A-8645-E21D2811037E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
@@ -15843,7 +15843,7 @@
         <v>613</v>
       </c>
       <c r="F399" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G399" t="s">
         <v>45</v>
@@ -15872,7 +15872,7 @@
         <v>612</v>
       </c>
       <c r="F400" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G400" t="s">
         <v>45</v>
@@ -16061,7 +16061,7 @@
         <v>171</v>
       </c>
       <c r="F406" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="G406" t="s">
         <v>45</v>
@@ -16183,7 +16183,7 @@
         <v>200</v>
       </c>
       <c r="F410" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G410" t="s">
         <v>286</v>
@@ -16212,7 +16212,7 @@
         <v>544</v>
       </c>
       <c r="F411" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G411" t="s">
         <v>286</v>
@@ -16270,7 +16270,7 @@
         <v>180</v>
       </c>
       <c r="F413" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G413" t="s">
         <v>286</v>
@@ -16299,7 +16299,7 @@
         <v>225</v>
       </c>
       <c r="F414" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G414" t="s">
         <v>286</v>
@@ -16328,7 +16328,7 @@
         <v>378</v>
       </c>
       <c r="F415" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G415" t="s">
         <v>286</v>
@@ -16357,7 +16357,7 @@
         <v>182</v>
       </c>
       <c r="F416" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G416" t="s">
         <v>286</v>
@@ -16418,7 +16418,7 @@
         <v>428</v>
       </c>
       <c r="F418" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G418" t="s">
         <v>286</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EAB7C5B-D10D-434A-8645-E21D2811037E}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48E8679-5897-44F0-B168-85583E779B7C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="9060" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15689,7 +15689,7 @@
         <v>312</v>
       </c>
       <c r="F394" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G394" t="s">
         <v>286</v>
@@ -15721,7 +15721,7 @@
         <v>298</v>
       </c>
       <c r="F395" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G395" t="s">
         <v>286</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48E8679-5897-44F0-B168-85583E779B7C}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18D29EC8-F2DF-49D3-A5E6-106E5D210BAD}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="9060" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="9240" yWindow="1530" windowWidth="9060" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13691,7 +13691,7 @@
         <v>710</v>
       </c>
       <c r="F337" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="G337" t="s">
         <v>97</v>

--- a/data/profile.xlsx
+++ b/data/profile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18D29EC8-F2DF-49D3-A5E6-106E5D210BAD}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{D077749A-49D6-43D1-ABD4-A2E8F0E01280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{888D9DC7-1C5E-44C9-833A-6BAD8383F4E1}"/>
   <bookViews>
-    <workbookView xWindow="9240" yWindow="1530" windowWidth="9060" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
+    <workbookView xWindow="4785" yWindow="1965" windowWidth="15015" windowHeight="13170" xr2:uid="{298304A4-FB78-45B5-B8F6-A597285BA23E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="1037">
   <si>
     <t>ナンバー</t>
     <phoneticPr fontId="1"/>
@@ -2492,6 +2492,1281 @@
   <si>
     <t>黒炭ひぐらし</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>肉全般</t>
+  </si>
+  <si>
+    <t>白米・海獣の肉・酒に合う物</t>
+  </si>
+  <si>
+    <t>秋島のサンマ・旬の魚</t>
+  </si>
+  <si>
+    <t>みかん・フルーツ全般</t>
+  </si>
+  <si>
+    <t>辛口海鮮パスタ・紅茶に合うもの</t>
+  </si>
+  <si>
+    <t>わたあめ・チョコレート・甘いもの全般</t>
+  </si>
+  <si>
+    <t>サンドウィッチ・甘すぎないケーキ・コーヒーに合うもの</t>
+  </si>
+  <si>
+    <t>ハンバーガー・フライドポテト・コーラに合うもの</t>
+  </si>
+  <si>
+    <t>カレー</t>
+  </si>
+  <si>
+    <t>バラ・ローズティー</t>
+  </si>
+  <si>
+    <t>レバー</t>
+  </si>
+  <si>
+    <t>チーズ</t>
+  </si>
+  <si>
+    <t>ヨーグルト</t>
+  </si>
+  <si>
+    <t>駄菓子</t>
+  </si>
+  <si>
+    <t>愛妻弁当</t>
+  </si>
+  <si>
+    <t>青椒肉絲</t>
+  </si>
+  <si>
+    <t>ドネルケバブ</t>
+  </si>
+  <si>
+    <t>すき焼き</t>
+  </si>
+  <si>
+    <t>ミートボール</t>
+  </si>
+  <si>
+    <t>ゆでタマゴ</t>
+  </si>
+  <si>
+    <t>キムチ炒飯・ロブスター</t>
+  </si>
+  <si>
+    <t>かまぼこ</t>
+  </si>
+  <si>
+    <t>旬の魚</t>
+  </si>
+  <si>
+    <t>鳥の骨つき肉</t>
+  </si>
+  <si>
+    <t>酒・安い食べ物</t>
+  </si>
+  <si>
+    <t>パイナップル</t>
+  </si>
+  <si>
+    <t>ブートジョロキアペペロンチーノ</t>
+  </si>
+  <si>
+    <t>あご出汁茶漬け</t>
+  </si>
+  <si>
+    <t>ジャガイモのフリット ローズマリー風味</t>
+  </si>
+  <si>
+    <t>チェリーパイ・ケバブ</t>
+  </si>
+  <si>
+    <t>おにぎり</t>
+  </si>
+  <si>
+    <t>お菓子・甘いもの全般</t>
+  </si>
+  <si>
+    <t>ドーナツ</t>
+  </si>
+  <si>
+    <t>スムージー</t>
+  </si>
+  <si>
+    <t>ビスケット</t>
+  </si>
+  <si>
+    <t>キャンディ、牛タン</t>
+  </si>
+  <si>
+    <t>ロイヤルミルクティー・バロット</t>
+  </si>
+  <si>
+    <t>魚人島のお菓子・ショコラタウンのチョコ</t>
+  </si>
+  <si>
+    <t>チキンライス</t>
+  </si>
+  <si>
+    <t>ゾウ肉のステーキ</t>
+  </si>
+  <si>
+    <t>野菜全般・トウモロコシ</t>
+  </si>
+  <si>
+    <t>プロテイン</t>
+  </si>
+  <si>
+    <t>ビーフステーキ(レア)</t>
+  </si>
+  <si>
+    <t>運任せの闇鍋</t>
+  </si>
+  <si>
+    <t>フカヒレのスープ</t>
+  </si>
+  <si>
+    <t>ロリポップキャンディ</t>
+  </si>
+  <si>
+    <t>若鳥のささ身</t>
+  </si>
+  <si>
+    <t>紹興酒</t>
+  </si>
+  <si>
+    <t>海王類の塩焼き</t>
+  </si>
+  <si>
+    <t>赤ワイン</t>
+  </si>
+  <si>
+    <t>爆弾の入っていないリンゴ</t>
+  </si>
+  <si>
+    <t>爆弾の入っていないニンジン</t>
+  </si>
+  <si>
+    <t>バナナ</t>
+  </si>
+  <si>
+    <t>はちみつ・サーモン</t>
+  </si>
+  <si>
+    <t>火鍋</t>
+  </si>
+  <si>
+    <t>ホットドック</t>
+  </si>
+  <si>
+    <t>母ーたんのキャビアおにぎり</t>
+  </si>
+  <si>
+    <t>ロブスター</t>
+  </si>
+  <si>
+    <t>ワニ肉・トマト</t>
+  </si>
+  <si>
+    <t>キャビアのマリネ</t>
+  </si>
+  <si>
+    <t>もずく酢・フルーツ</t>
+  </si>
+  <si>
+    <t>おにぎり・焼き魚</t>
+  </si>
+  <si>
+    <t>つけもの</t>
+  </si>
+  <si>
+    <t>ポップコーン</t>
+  </si>
+  <si>
+    <t>肉</t>
+  </si>
+  <si>
+    <t>小籠包</t>
+  </si>
+  <si>
+    <t>かき氷</t>
+  </si>
+  <si>
+    <t>ハンバーガーセット（ハンバーガー・ポテト・いちごシェイク）</t>
+  </si>
+  <si>
+    <t>ソーセージ</t>
+  </si>
+  <si>
+    <t>石焼ビビンバ</t>
+  </si>
+  <si>
+    <t>レタス・キャベツ・梅干し</t>
+  </si>
+  <si>
+    <t>グレープ</t>
+  </si>
+  <si>
+    <t>抹茶ミルクかき氷</t>
+  </si>
+  <si>
+    <t>アート映えするスイーツ</t>
+  </si>
+  <si>
+    <t>熟成肉のステーキ</t>
+  </si>
+  <si>
+    <t>ルシアンの手料理・ギムレット（カクテル）</t>
+  </si>
+  <si>
+    <t>ピザ</t>
+  </si>
+  <si>
+    <t>高い酒・オートキュイジーヌ</t>
+  </si>
+  <si>
+    <t>パンキッシュ</t>
+  </si>
+  <si>
+    <t>3段アイスクリーム</t>
+  </si>
+  <si>
+    <t>ベビーカステラ</t>
+  </si>
+  <si>
+    <t>牛骨スープ・豚骨料理</t>
+  </si>
+  <si>
+    <t>ロールキャベツ</t>
+  </si>
+  <si>
+    <t>ペペロンチーノ</t>
+  </si>
+  <si>
+    <t>フォーチュンクッキー</t>
+  </si>
+  <si>
+    <t>海王類の肉とトマトの煮込み</t>
+  </si>
+  <si>
+    <t>肉団子・トマト</t>
+  </si>
+  <si>
+    <t>海獣の肉入りカルツォーネ</t>
+  </si>
+  <si>
+    <t>トムヤムクン</t>
+  </si>
+  <si>
+    <t>あずき・豚肉</t>
+  </si>
+  <si>
+    <t>美肌効果のあるベリー・ベリー酒</t>
+  </si>
+  <si>
+    <t>仔牛のレバー</t>
+  </si>
+  <si>
+    <t>キノコのスパゲティ</t>
+  </si>
+  <si>
+    <t>フィッシュ&amp;チップス</t>
+  </si>
+  <si>
+    <t>焼き魚</t>
+  </si>
+  <si>
+    <t>海王類の丸焼き</t>
+  </si>
+  <si>
+    <t>ホタテ</t>
+  </si>
+  <si>
+    <t>サンジが作ったピラフ</t>
+  </si>
+  <si>
+    <t>牛の丸焼き</t>
+  </si>
+  <si>
+    <t>たこ焼き・たこ焼き煎餅</t>
+  </si>
+  <si>
+    <t>エビの刺身</t>
+  </si>
+  <si>
+    <t>アサリの味噌汁</t>
+  </si>
+  <si>
+    <t>焼いた家(ウェルダン)</t>
+  </si>
+  <si>
+    <t>栗きんとん</t>
+  </si>
+  <si>
+    <t>高級菓子</t>
+  </si>
+  <si>
+    <t>昼間から飲む酒</t>
+  </si>
+  <si>
+    <t>ランブータン</t>
+  </si>
+  <si>
+    <t>たぬきそば</t>
+  </si>
+  <si>
+    <t>ビール・から揚げ</t>
+  </si>
+  <si>
+    <t>みそ汁</t>
+  </si>
+  <si>
+    <t>オレンジサワー</t>
+  </si>
+  <si>
+    <t>生ビール</t>
+  </si>
+  <si>
+    <t>牛の左バラ肉</t>
+  </si>
+  <si>
+    <t>炭酸飲料</t>
+  </si>
+  <si>
+    <t>キュウリ</t>
+  </si>
+  <si>
+    <t>アイスクリーム</t>
+  </si>
+  <si>
+    <t>ババーのミートパイ</t>
+  </si>
+  <si>
+    <t>キャンディ</t>
+  </si>
+  <si>
+    <t>豚の丸焼き・サメ</t>
+  </si>
+  <si>
+    <t>スイカ</t>
+  </si>
+  <si>
+    <t>ペロリンキャンディ</t>
+  </si>
+  <si>
+    <t>タイ焼き</t>
+  </si>
+  <si>
+    <t>海獣の肉</t>
+  </si>
+  <si>
+    <t>イカナゴ</t>
+  </si>
+  <si>
+    <t>巨魚の骨</t>
+  </si>
+  <si>
+    <t>うなぎの蒲焼</t>
+  </si>
+  <si>
+    <t>タコワサ</t>
+  </si>
+  <si>
+    <t>酒、肴になるもの、二日酔い時のしじみ汁</t>
+  </si>
+  <si>
+    <t>カニ</t>
+  </si>
+  <si>
+    <t>サザエのつぼ焼き</t>
+  </si>
+  <si>
+    <t>ビール・首長竜の肉</t>
+  </si>
+  <si>
+    <t>ヒガシザメのステーキ</t>
+  </si>
+  <si>
+    <t>ビール・トリケラトプスの肉</t>
+  </si>
+  <si>
+    <t>ハチミツ</t>
+  </si>
+  <si>
+    <t>ウォッカ・高級料理</t>
+  </si>
+  <si>
+    <t>とんかつ</t>
+  </si>
+  <si>
+    <t>鶏のキモ</t>
+  </si>
+  <si>
+    <t>マグロの右ほほ肉</t>
+  </si>
+  <si>
+    <t>ラーメン</t>
+  </si>
+  <si>
+    <t>ボカディート</t>
+  </si>
+  <si>
+    <t>バーニャカウダ</t>
+  </si>
+  <si>
+    <t>ホルモン焼き</t>
+  </si>
+  <si>
+    <t>アーモンド</t>
+  </si>
+  <si>
+    <t>ハンバーグ</t>
+  </si>
+  <si>
+    <t>ウインナー</t>
+  </si>
+  <si>
+    <t>ガーリックシュリンプ</t>
+  </si>
+  <si>
+    <t>五目ちまき</t>
+  </si>
+  <si>
+    <t>最高級のシャンパン</t>
+  </si>
+  <si>
+    <t>瓦せんべい</t>
+  </si>
+  <si>
+    <t>ジュース・ケーキ・子供と一緒に楽しめるもの</t>
+  </si>
+  <si>
+    <t>牛乳・卵焼き</t>
+  </si>
+  <si>
+    <t>酒・山菜・熊肉</t>
+  </si>
+  <si>
+    <t>野牛の肉</t>
+  </si>
+  <si>
+    <t>道場の縁側で食べるスイカ</t>
+  </si>
+  <si>
+    <t>サーモン</t>
+  </si>
+  <si>
+    <t>ドッグフード</t>
+  </si>
+  <si>
+    <t>珍獣島で採れるメロン</t>
+  </si>
+  <si>
+    <t>魚介類</t>
+  </si>
+  <si>
+    <t>にんじんジュース</t>
+  </si>
+  <si>
+    <t>ピーマンの肉詰め</t>
+  </si>
+  <si>
+    <t>オニオンリングフライ</t>
+  </si>
+  <si>
+    <t>激辛チキンウイング</t>
+  </si>
+  <si>
+    <t>プリン</t>
+  </si>
+  <si>
+    <t>ローストビーフ</t>
+  </si>
+  <si>
+    <t>みかん</t>
+  </si>
+  <si>
+    <t>生ハムメロン</t>
+  </si>
+  <si>
+    <t>もやし炒め</t>
+  </si>
+  <si>
+    <t>ポテチ</t>
+  </si>
+  <si>
+    <t>一本うどん</t>
+  </si>
+  <si>
+    <t>はちみつ・ビターチョコレート</t>
+  </si>
+  <si>
+    <t>モンブラン・カボチャのケーキ</t>
+  </si>
+  <si>
+    <t>コーヒー・シュガートースト</t>
+  </si>
+  <si>
+    <t>大王イカ焼き</t>
+  </si>
+  <si>
+    <t>大王イカ</t>
+  </si>
+  <si>
+    <t>栗ごはん</t>
+  </si>
+  <si>
+    <t>リ〜ンゴ</t>
+  </si>
+  <si>
+    <t>大根の桜漬け</t>
+  </si>
+  <si>
+    <t>酒・梅干し</t>
+  </si>
+  <si>
+    <t>ミルク</t>
+  </si>
+  <si>
+    <t>ウイスキー</t>
+  </si>
+  <si>
+    <t>煮豆</t>
+  </si>
+  <si>
+    <t>豚足</t>
+  </si>
+  <si>
+    <t>海藻サラダ</t>
+  </si>
+  <si>
+    <t>海藻マリネ</t>
+  </si>
+  <si>
+    <t>イカ</t>
+  </si>
+  <si>
+    <t>アワビのステーキ</t>
+  </si>
+  <si>
+    <t>もずくのスープ</t>
+  </si>
+  <si>
+    <t>海葡萄のパスタ</t>
+  </si>
+  <si>
+    <t>海牛のミルク</t>
+  </si>
+  <si>
+    <t>アザラシ</t>
+  </si>
+  <si>
+    <t>ホタテサンド</t>
+  </si>
+  <si>
+    <t>シジミピザ</t>
+  </si>
+  <si>
+    <t>ケイミーがくれる蛤</t>
+  </si>
+  <si>
+    <t>ワカメブリュレ</t>
+  </si>
+  <si>
+    <t>バラジャム入りの紅茶</t>
+  </si>
+  <si>
+    <t>馬肉</t>
+  </si>
+  <si>
+    <t>三ツ葉とアサリの炊き込みご飯</t>
+  </si>
+  <si>
+    <t>ブドウ糖・ガスパチョ</t>
+  </si>
+  <si>
+    <t>ウィスキー・焼き鳥</t>
+  </si>
+  <si>
+    <t>ガスパチョ</t>
+  </si>
+  <si>
+    <t>スコッチ・スコッチエッグ</t>
+  </si>
+  <si>
+    <t>貝料理</t>
+  </si>
+  <si>
+    <t>兵隊さんの手作りケーキ</t>
+  </si>
+  <si>
+    <t>クレマカタラナ</t>
+  </si>
+  <si>
+    <t>フルーツパンチ</t>
+  </si>
+  <si>
+    <t>カボチャ</t>
+  </si>
+  <si>
+    <t>ジョッキー杯の生卵</t>
+  </si>
+  <si>
+    <t>サーロインステーキ</t>
+  </si>
+  <si>
+    <t>空島のりんご・巨大ワカメ</t>
+  </si>
+  <si>
+    <t>はんぺん</t>
+  </si>
+  <si>
+    <t>牛すじ</t>
+  </si>
+  <si>
+    <t>たまご</t>
+  </si>
+  <si>
+    <t>きんちゃくもち</t>
+  </si>
+  <si>
+    <t>おでんの全て</t>
+  </si>
+  <si>
+    <t>ナチョス</t>
+  </si>
+  <si>
+    <t>ツイストポテト</t>
+  </si>
+  <si>
+    <t>カニのパエリア</t>
+  </si>
+  <si>
+    <t>みたらし団子</t>
+  </si>
+  <si>
+    <t>アスパラガス</t>
+  </si>
+  <si>
+    <t>おしるこ、りんご</t>
+  </si>
+  <si>
+    <t>サン五郎の十八番そば</t>
+  </si>
+  <si>
+    <t>白米</t>
+  </si>
+  <si>
+    <t>カッパ巻き</t>
+  </si>
+  <si>
+    <t>こんぶ巻き</t>
+  </si>
+  <si>
+    <t>三食だんご</t>
+  </si>
+  <si>
+    <t>大吟醸</t>
+  </si>
+  <si>
+    <t>がんもどき</t>
+  </si>
+  <si>
+    <t>おでん、サーモン(生まるかじり)</t>
+  </si>
+  <si>
+    <t>酒、魚の皮</t>
+  </si>
+  <si>
+    <t>トビウオの刺身</t>
+  </si>
+  <si>
+    <t>おしるこ</t>
+  </si>
+  <si>
+    <t>ヤシオリの酒、サンマ</t>
+  </si>
+  <si>
+    <t>ウーロンハイ</t>
+  </si>
+  <si>
+    <t>リンゴ(丸かじり)</t>
+  </si>
+  <si>
+    <t>油揚げ</t>
+  </si>
+  <si>
+    <t>もみじまんじゅう</t>
+  </si>
+  <si>
+    <t>ナス</t>
+  </si>
+  <si>
+    <t>(ホルモン焼き)</t>
+  </si>
+  <si>
+    <t>大福</t>
+  </si>
+  <si>
+    <t>巻物</t>
+  </si>
+  <si>
+    <t>山芋</t>
+  </si>
+  <si>
+    <t>納豆</t>
+  </si>
+  <si>
+    <t>おはぎ</t>
+  </si>
+  <si>
+    <t>びわようかん</t>
+  </si>
+  <si>
+    <t>ふ菓子</t>
+  </si>
+  <si>
+    <t>サルナシ</t>
+  </si>
+  <si>
+    <t>ちょこれいと</t>
+  </si>
+  <si>
+    <t>すいとん</t>
+  </si>
+  <si>
+    <t>串揚げ</t>
+  </si>
+  <si>
+    <t>火薬茶・上質な火薬・かやくご飯</t>
+  </si>
+  <si>
+    <t>レモンティー・チョコレート</t>
+  </si>
+  <si>
+    <t>オレンジペコ</t>
+  </si>
+  <si>
+    <t>アップルティー・ピザ</t>
+  </si>
+  <si>
+    <t>ハーブティー</t>
+  </si>
+  <si>
+    <t>マテ茶・生ハム</t>
+  </si>
+  <si>
+    <t>ワルサギの焼き鳥・ユバの水</t>
+  </si>
+  <si>
+    <t>赤ワイン(イテュルツブルガー・シュタイン）</t>
+  </si>
+  <si>
+    <t>空豆茶</t>
+  </si>
+  <si>
+    <t>パンプキンコーヒー</t>
+  </si>
+  <si>
+    <t>スカイロブスター</t>
+  </si>
+  <si>
+    <t>飴雲</t>
+  </si>
+  <si>
+    <t>酒・山菜・雲グマ肉</t>
+  </si>
+  <si>
+    <t>バーベキュー</t>
+  </si>
+  <si>
+    <t>雲豹の肉</t>
+  </si>
+  <si>
+    <t>空サメのジャーキー</t>
+  </si>
+  <si>
+    <t>空ひじきと空大豆の煮物</t>
+  </si>
+  <si>
+    <t>カボチャ麺</t>
+  </si>
+  <si>
+    <t>空鶏のササミ</t>
+  </si>
+  <si>
+    <t>白玉入り空島ぜんざい</t>
+  </si>
+  <si>
+    <t>空貝紐の甘辛炒め</t>
+  </si>
+  <si>
+    <t>空トカゲ</t>
+  </si>
+  <si>
+    <t>ゴローの手作りサンドイッチ</t>
+  </si>
+  <si>
+    <t>空ビラメのムニエル</t>
+  </si>
+  <si>
+    <t>カボチャのジュース</t>
+  </si>
+  <si>
+    <t>大魚の丸焼き</t>
+  </si>
+  <si>
+    <t>ココロの作ったカレー</t>
+  </si>
+  <si>
+    <t>ほうれん草</t>
+  </si>
+  <si>
+    <t>苺のリキュール・イワシの酢漬け</t>
+  </si>
+  <si>
+    <t>天ぷらうどん</t>
+  </si>
+  <si>
+    <t>フルーツサンドイッチ</t>
+  </si>
+  <si>
+    <t>チョコレートサンデー</t>
+  </si>
+  <si>
+    <t>ココロの作ったラーメン</t>
+  </si>
+  <si>
+    <t>バナナ・カステラ</t>
+  </si>
+  <si>
+    <t>クジラの丸焼き</t>
+  </si>
+  <si>
+    <t>ラム肉のピリ辛炒め</t>
+  </si>
+  <si>
+    <t>ブランデー</t>
+  </si>
+  <si>
+    <t>ミルクシェイク</t>
+  </si>
+  <si>
+    <t>巻きずし・トルネードポテト</t>
+  </si>
+  <si>
+    <t>優しい味の精進料理</t>
+  </si>
+  <si>
+    <t>目玉焼き</t>
+  </si>
+  <si>
+    <t>ハバネロの肉詰め</t>
+  </si>
+  <si>
+    <t>子羊のロースト</t>
+  </si>
+  <si>
+    <t>チャパティ</t>
+  </si>
+  <si>
+    <t>酒・味噌汁</t>
+  </si>
+  <si>
+    <t>ウィスキー・高級ビーフステーキ</t>
+  </si>
+  <si>
+    <t>ぶりの刺身</t>
+  </si>
+  <si>
+    <t>ピッツァ・マルゲリータ</t>
+  </si>
+  <si>
+    <t>スープスパゲティ</t>
+  </si>
+  <si>
+    <t>シマウマの丸焼き</t>
+  </si>
+  <si>
+    <t>ベーグルサンド・ホットココア</t>
+  </si>
+  <si>
+    <t>チョコレートフォンデュ</t>
+  </si>
+  <si>
+    <t>ブランマンジェ</t>
+  </si>
+  <si>
+    <t>モカチョコレート・おもち</t>
+  </si>
+  <si>
+    <t>白桃・おでん</t>
+  </si>
+  <si>
+    <t>刺身のレタス巻・ロールキャベツ</t>
+  </si>
+  <si>
+    <t>鮫肉のハーブ焼き</t>
+  </si>
+  <si>
+    <t>お鶴のおしるこ・大根</t>
+  </si>
+  <si>
+    <t>アボカド・アイスクリーム</t>
+  </si>
+  <si>
+    <t>骨</t>
+  </si>
+  <si>
+    <t>カバの肉</t>
+  </si>
+  <si>
+    <t>トカゲの肉</t>
+  </si>
+  <si>
+    <t>ヘビの肉</t>
+  </si>
+  <si>
+    <t>骨・手羽肉</t>
+  </si>
+  <si>
+    <t>ラザニア・かまぼこ</t>
+  </si>
+  <si>
+    <t>ラザニア・骨</t>
+  </si>
+  <si>
+    <t>グリーンピース</t>
+  </si>
+  <si>
+    <t>ヨロイオコゼの毒・リンゴ</t>
+  </si>
+  <si>
+    <t>アサリのスープ</t>
+  </si>
+  <si>
+    <t>アップルジュース・パウンドケーキ</t>
+  </si>
+  <si>
+    <t>オマール海老のトマトパスタ</t>
+  </si>
+  <si>
+    <t>チョコレートシフォンケーキ</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>イチゴ・ウイスキー</t>
+  </si>
+  <si>
+    <t>ブルーベリー・スコッチ</t>
+  </si>
+  <si>
+    <t>ハンバーグ・マカロン</t>
+  </si>
+  <si>
+    <t>海王類の肉・ラム酒</t>
+  </si>
+  <si>
+    <t>ウォーランド近海の巨大魚・ラム酒</t>
+  </si>
+  <si>
+    <t>生チョコレート・プリン</t>
+  </si>
+  <si>
+    <t>お茶と茶菓子</t>
+  </si>
+  <si>
+    <t>海軍おかき</t>
+  </si>
+  <si>
+    <t>シェリー酒(ティオペペ) ・酪農牛乳・コーヒー（クザンオリジナルブランド）</t>
+  </si>
+  <si>
+    <t>せんべい・カレー</t>
+  </si>
+  <si>
+    <t>キャビアの金箔のせ</t>
+  </si>
+  <si>
+    <t>サルの脳みそ</t>
+  </si>
+  <si>
+    <t>高級ソフトクリーム</t>
+  </si>
+  <si>
+    <t>カレー・プリン・ムルキーヤ</t>
+  </si>
+  <si>
+    <t>ちくわ</t>
+  </si>
+  <si>
+    <t>サボテン</t>
+  </si>
+  <si>
+    <t>冷たい水・ボルティ</t>
+  </si>
+  <si>
+    <t>カルカデ</t>
+  </si>
+  <si>
+    <t>メハラビア</t>
+  </si>
+  <si>
+    <t>バーボン</t>
+  </si>
+  <si>
+    <t>コナーファ</t>
+  </si>
+  <si>
+    <t>鶏肉料理・コフタ</t>
+  </si>
+  <si>
+    <t>バナナ・コシャリ</t>
+  </si>
+  <si>
+    <t>ケバブ・シャンパン</t>
+  </si>
+  <si>
+    <t>サモサ</t>
+  </si>
+  <si>
+    <t>青海から仕入れたお茶菓子</t>
+  </si>
+  <si>
+    <t>餃子</t>
+  </si>
+  <si>
+    <t>海王類の角煮</t>
+  </si>
+  <si>
+    <t>アップルクランブル</t>
+  </si>
+  <si>
+    <t>ガム</t>
+  </si>
+  <si>
+    <t>トンカツ</t>
+  </si>
+  <si>
+    <t>毒のスープ・フグの刺身【毒抜きなし】</t>
+  </si>
+  <si>
+    <t>プルコギ</t>
+  </si>
+  <si>
+    <t>囚人のスクリーム（悲鳴）</t>
+  </si>
+  <si>
+    <t>白米・とうがらし</t>
+  </si>
+  <si>
+    <t>メロン</t>
+  </si>
+  <si>
+    <t>ラム・チョコレート</t>
+  </si>
+  <si>
+    <t>焼き菓子</t>
+  </si>
+  <si>
+    <t>豆大福</t>
+  </si>
+  <si>
+    <t>クレームブリュレ・ドーナツ</t>
+  </si>
+  <si>
+    <t>どんぐり</t>
+  </si>
+  <si>
+    <t>トナカイの肉</t>
+  </si>
+  <si>
+    <t>しらたき</t>
+  </si>
+  <si>
+    <t>おにぎりと焼き芋</t>
+  </si>
+  <si>
+    <t>タコパフェ・釜炒り茶</t>
+  </si>
+  <si>
+    <t>焼きナス</t>
+  </si>
+  <si>
+    <t>ふかしたサツマイモ</t>
+  </si>
+  <si>
+    <t>ニンジン</t>
+  </si>
+  <si>
+    <t>みそラーメン、しょうが、バナナ</t>
+  </si>
+  <si>
+    <t>うどん&amp;そば</t>
+  </si>
+  <si>
+    <t>スモークチキン</t>
+  </si>
+  <si>
+    <t>ホットコーヒー</t>
+  </si>
+  <si>
+    <t>リカが作ったおにぎり、ジャガバター</t>
+  </si>
+  <si>
+    <t>豪華なステーキ、キャビア</t>
+  </si>
+  <si>
+    <t>高級な料理</t>
+  </si>
+  <si>
+    <t>紅茶（アールグレイ）、紅茶に合うクッキー</t>
+  </si>
+  <si>
+    <t>せんべい、緑茶</t>
+  </si>
+  <si>
+    <t>リンゴ、バナナ</t>
+  </si>
+  <si>
+    <t>サンジのパイユ</t>
+  </si>
+  <si>
+    <t>魚［本当はニンジン］</t>
+  </si>
+  <si>
+    <t>酒全般、海藻サラダ</t>
+  </si>
+  <si>
+    <t>白米、海獣の肉、酒に合う物</t>
+  </si>
+  <si>
+    <t>アップルパイ</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>ナミの作る雷雲</t>
+  </si>
+  <si>
+    <t>人参</t>
+  </si>
+  <si>
+    <t>シーザーのキャンディ</t>
+  </si>
+  <si>
+    <t>侵入者の肉</t>
+  </si>
+  <si>
+    <t>熊鍋</t>
+  </si>
+  <si>
+    <t>肉全般、ワニ肉</t>
+  </si>
+  <si>
+    <t>人間</t>
+  </si>
+  <si>
+    <t>海王類の肉</t>
+  </si>
+  <si>
+    <t>食べられれば何でも</t>
+  </si>
+  <si>
+    <t>人間の骨</t>
+  </si>
+  <si>
+    <t>草（特にアジサイ）</t>
+  </si>
+  <si>
+    <t>魚（特にイワシ）</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>トマトの離乳食</t>
+  </si>
+  <si>
+    <t>白米、きつねうどん</t>
+  </si>
+  <si>
+    <t>天ぷらそば</t>
+  </si>
+  <si>
+    <t>おむすび、団子</t>
+  </si>
+  <si>
+    <t>清酒、海獣の刺身</t>
+  </si>
+  <si>
+    <t>もみじまんじゅう、すき焼き</t>
+  </si>
+  <si>
+    <t>フォアグラ→海藻マリネ</t>
+  </si>
+  <si>
+    <t>びわ</t>
+  </si>
+  <si>
+    <t>泡盛</t>
+  </si>
+  <si>
+    <t>ビッグ・マムのソウル</t>
+  </si>
+  <si>
+    <t>ゼウス先輩</t>
+  </si>
+  <si>
+    <t>にんにく</t>
+  </si>
+  <si>
+    <t>熟成した酒（面倒だから食事はしない）</t>
+  </si>
+  <si>
+    <t>りんごパイ、コーヒー、マカロニスパゲティ</t>
+  </si>
+  <si>
+    <t>乳粥</t>
+  </si>
+  <si>
+    <t>悪魔風チキンステーキ</t>
+  </si>
+  <si>
+    <t>パイとコーヒー（基本、食事は欲に任せる）</t>
+  </si>
+  <si>
+    <t>野菜ジュース（基本、食事は欲に任せる）</t>
+  </si>
+  <si>
+    <t>カレーライス</t>
+  </si>
+  <si>
+    <t>ハンバーガー</t>
+  </si>
+  <si>
+    <t>骨付き肉</t>
+  </si>
+  <si>
+    <t>イチゴシャーベット（ピザは作りすぎて飽きた）</t>
+  </si>
+  <si>
+    <t>蜂蜜</t>
+  </si>
+  <si>
+    <t>ポテトチップス</t>
+  </si>
+  <si>
+    <t>ジュースと洋菓子</t>
+  </si>
+  <si>
+    <t>ぶどうジュース</t>
   </si>
 </sst>
 </file>
@@ -2859,13 +4134,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36AD3A8C-E295-4560-9C61-1E069B2F26F7}">
-  <dimension ref="A1:R455"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="29.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2917,11 +4192,11 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2956,10 +4231,13 @@
         <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+        <v>612</v>
+      </c>
+      <c r="S2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2994,10 +4272,13 @@
         <v>22</v>
       </c>
       <c r="R3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+        <v>613</v>
+      </c>
+      <c r="S3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3038,10 +4319,13 @@
         <v>29</v>
       </c>
       <c r="R4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>614</v>
+      </c>
+      <c r="S4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3070,10 +4354,13 @@
         <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+        <v>615</v>
+      </c>
+      <c r="S5" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3108,10 +4395,13 @@
         <v>21</v>
       </c>
       <c r="R6" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+        <v>616</v>
+      </c>
+      <c r="S6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3155,10 +4445,13 @@
         <v>43</v>
       </c>
       <c r="R7" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+        <v>617</v>
+      </c>
+      <c r="S7" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3187,10 +4480,13 @@
         <v>20</v>
       </c>
       <c r="R8" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+        <v>618</v>
+      </c>
+      <c r="S8" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3222,10 +4518,13 @@
         <v>28</v>
       </c>
       <c r="R9" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+        <v>619</v>
+      </c>
+      <c r="S9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3251,10 +4550,13 @@
         <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+        <v>620</v>
+      </c>
+      <c r="S10" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3283,10 +4585,13 @@
         <v>20</v>
       </c>
       <c r="R11" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+        <v>621</v>
+      </c>
+      <c r="S11" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>9</v>
       </c>
@@ -3315,10 +4620,13 @@
         <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+        <v>622</v>
+      </c>
+      <c r="S12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>10</v>
       </c>
@@ -3347,10 +4655,13 @@
         <v>20</v>
       </c>
       <c r="R13" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+        <v>623</v>
+      </c>
+      <c r="S13" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>11</v>
       </c>
@@ -3379,10 +4690,13 @@
         <v>57</v>
       </c>
       <c r="R14" t="s">
+        <v>624</v>
+      </c>
+      <c r="S14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>12</v>
       </c>
@@ -3411,10 +4725,13 @@
         <v>57</v>
       </c>
       <c r="R15" t="s">
+        <v>625</v>
+      </c>
+      <c r="S15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>13</v>
       </c>
@@ -3449,10 +4766,13 @@
         <v>28</v>
       </c>
       <c r="R16" t="s">
+        <v>626</v>
+      </c>
+      <c r="S16" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3487,10 +4807,13 @@
         <v>74</v>
       </c>
       <c r="R17" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+        <v>627</v>
+      </c>
+      <c r="S17" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3528,10 +4851,13 @@
         <v>41</v>
       </c>
       <c r="R18" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+        <v>628</v>
+      </c>
+      <c r="S18" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3569,10 +4895,13 @@
         <v>41</v>
       </c>
       <c r="R19" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+        <v>629</v>
+      </c>
+      <c r="S19" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3601,10 +4930,13 @@
         <v>20</v>
       </c>
       <c r="R20" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+        <v>630</v>
+      </c>
+      <c r="S20" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3639,10 +4971,13 @@
         <v>73</v>
       </c>
       <c r="R21" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+        <v>631</v>
+      </c>
+      <c r="S21" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3671,10 +5006,13 @@
         <v>20</v>
       </c>
       <c r="R22" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+        <v>632</v>
+      </c>
+      <c r="S22" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3706,10 +5044,13 @@
         <v>73</v>
       </c>
       <c r="R23" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+        <v>633</v>
+      </c>
+      <c r="S23" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3738,10 +5079,13 @@
         <v>20</v>
       </c>
       <c r="R24" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+        <v>634</v>
+      </c>
+      <c r="S24" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>28</v>
       </c>
@@ -3770,10 +5114,13 @@
         <v>20</v>
       </c>
       <c r="R25" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
+        <v>635</v>
+      </c>
+      <c r="S25" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>29</v>
       </c>
@@ -3802,10 +5149,13 @@
         <v>34</v>
       </c>
       <c r="R26" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+        <v>636</v>
+      </c>
+      <c r="S26" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>34</v>
       </c>
@@ -3837,10 +5187,13 @@
         <v>21</v>
       </c>
       <c r="R27" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+        <v>637</v>
+      </c>
+      <c r="S27" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>37</v>
       </c>
@@ -3872,10 +5225,13 @@
         <v>73</v>
       </c>
       <c r="R28" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+        <v>638</v>
+      </c>
+      <c r="S28" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>40</v>
       </c>
@@ -3907,10 +5263,13 @@
         <v>21</v>
       </c>
       <c r="R29" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+        <v>639</v>
+      </c>
+      <c r="S29" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>41</v>
       </c>
@@ -3942,10 +5301,13 @@
         <v>91</v>
       </c>
       <c r="R30" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+        <v>640</v>
+      </c>
+      <c r="S30" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3974,10 +5336,13 @@
         <v>20</v>
       </c>
       <c r="R31" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+        <v>641</v>
+      </c>
+      <c r="S31" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>46</v>
       </c>
@@ -4006,10 +5371,13 @@
         <v>20</v>
       </c>
       <c r="R32" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
+        <v>642</v>
+      </c>
+      <c r="S32" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>49</v>
       </c>
@@ -4035,10 +5403,13 @@
         <v>20</v>
       </c>
       <c r="R33" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
+        <v>643</v>
+      </c>
+      <c r="S33" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>49</v>
       </c>
@@ -4064,10 +5435,13 @@
         <v>20</v>
       </c>
       <c r="R34" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
+        <v>644</v>
+      </c>
+      <c r="S34" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>51</v>
       </c>
@@ -4096,10 +5470,13 @@
         <v>20</v>
       </c>
       <c r="R35" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.4">
+        <v>645</v>
+      </c>
+      <c r="S35" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>52</v>
       </c>
@@ -4128,10 +5505,13 @@
         <v>20</v>
       </c>
       <c r="R36" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="S36" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>55</v>
       </c>
@@ -4160,10 +5540,13 @@
         <v>20</v>
       </c>
       <c r="R37" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
+        <v>647</v>
+      </c>
+      <c r="S37" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>57</v>
       </c>
@@ -4192,10 +5575,13 @@
         <v>20</v>
       </c>
       <c r="R38" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
+        <v>648</v>
+      </c>
+      <c r="S38" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>59</v>
       </c>
@@ -4224,10 +5610,13 @@
         <v>20</v>
       </c>
       <c r="R39" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.4">
+        <v>649</v>
+      </c>
+      <c r="S39" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>60</v>
       </c>
@@ -4256,10 +5645,13 @@
         <v>20</v>
       </c>
       <c r="R40" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
+        <v>650</v>
+      </c>
+      <c r="S40" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>61</v>
       </c>
@@ -4288,10 +5680,13 @@
         <v>20</v>
       </c>
       <c r="R41" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.4">
+        <v>651</v>
+      </c>
+      <c r="S41" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>62</v>
       </c>
@@ -4317,10 +5712,13 @@
         <v>20</v>
       </c>
       <c r="R42" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.4">
+        <v>652</v>
+      </c>
+      <c r="S42" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>63</v>
       </c>
@@ -4349,10 +5747,13 @@
         <v>34</v>
       </c>
       <c r="R43" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.4">
+        <v>653</v>
+      </c>
+      <c r="S43" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>66</v>
       </c>
@@ -4381,10 +5782,13 @@
         <v>20</v>
       </c>
       <c r="R44" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.4">
+        <v>654</v>
+      </c>
+      <c r="S44" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>67</v>
       </c>
@@ -4413,10 +5817,13 @@
         <v>20</v>
       </c>
       <c r="R45" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.4">
+        <v>655</v>
+      </c>
+      <c r="S45" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>68</v>
       </c>
@@ -4445,10 +5852,13 @@
         <v>20</v>
       </c>
       <c r="R46" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.4">
+        <v>656</v>
+      </c>
+      <c r="S46" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>71</v>
       </c>
@@ -4477,10 +5887,13 @@
         <v>20</v>
       </c>
       <c r="R47" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.4">
+        <v>657</v>
+      </c>
+      <c r="S47" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>72</v>
       </c>
@@ -4509,10 +5922,13 @@
         <v>20</v>
       </c>
       <c r="R48" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.4">
+        <v>658</v>
+      </c>
+      <c r="S48" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>73</v>
       </c>
@@ -4541,10 +5957,13 @@
         <v>20</v>
       </c>
       <c r="R49" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.4">
+        <v>659</v>
+      </c>
+      <c r="S49" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>76</v>
       </c>
@@ -4570,10 +5989,13 @@
         <v>20</v>
       </c>
       <c r="R50" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.4">
+        <v>660</v>
+      </c>
+      <c r="S50" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>78</v>
       </c>
@@ -4599,10 +6021,13 @@
         <v>20</v>
       </c>
       <c r="R51" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.4">
+        <v>661</v>
+      </c>
+      <c r="S51" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>80</v>
       </c>
@@ -4627,8 +6052,11 @@
       <c r="I52" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R52" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>81</v>
       </c>
@@ -4654,10 +6082,13 @@
         <v>20</v>
       </c>
       <c r="R53" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.4">
+        <v>663</v>
+      </c>
+      <c r="S53" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>82</v>
       </c>
@@ -4683,10 +6114,13 @@
         <v>20</v>
       </c>
       <c r="R54" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.4">
+        <v>664</v>
+      </c>
+      <c r="S54" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>84</v>
       </c>
@@ -4712,10 +6146,13 @@
         <v>20</v>
       </c>
       <c r="R55" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.4">
+        <v>665</v>
+      </c>
+      <c r="S55" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>85</v>
       </c>
@@ -4741,10 +6178,13 @@
         <v>20</v>
       </c>
       <c r="R56" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.4">
+        <v>666</v>
+      </c>
+      <c r="S56" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>86</v>
       </c>
@@ -4770,10 +6210,13 @@
         <v>20</v>
       </c>
       <c r="R57" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.4">
+        <v>667</v>
+      </c>
+      <c r="S57" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>93</v>
       </c>
@@ -4799,10 +6242,13 @@
         <v>20</v>
       </c>
       <c r="R58" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.4">
+        <v>668</v>
+      </c>
+      <c r="S58" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>94</v>
       </c>
@@ -4831,10 +6277,13 @@
         <v>20</v>
       </c>
       <c r="R59" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.4">
+        <v>669</v>
+      </c>
+      <c r="S59" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>95</v>
       </c>
@@ -4863,10 +6312,13 @@
         <v>20</v>
       </c>
       <c r="R60" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.4">
+        <v>670</v>
+      </c>
+      <c r="S60" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>97</v>
       </c>
@@ -4895,10 +6347,13 @@
         <v>34</v>
       </c>
       <c r="R61" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.4">
+        <v>671</v>
+      </c>
+      <c r="S61" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>98</v>
       </c>
@@ -4927,10 +6382,13 @@
         <v>20</v>
       </c>
       <c r="R62" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.4">
+        <v>672</v>
+      </c>
+      <c r="S62" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>101</v>
       </c>
@@ -4956,10 +6414,13 @@
         <v>20</v>
       </c>
       <c r="R63" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.4">
+        <v>673</v>
+      </c>
+      <c r="S63" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>102</v>
       </c>
@@ -4988,10 +6449,13 @@
         <v>20</v>
       </c>
       <c r="R64" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.4">
+        <v>674</v>
+      </c>
+      <c r="S64" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>103</v>
       </c>
@@ -5020,10 +6484,13 @@
         <v>20</v>
       </c>
       <c r="R65" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.4">
+        <v>675</v>
+      </c>
+      <c r="S65" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>107</v>
       </c>
@@ -5052,10 +6519,13 @@
         <v>34</v>
       </c>
       <c r="R66" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.4">
+        <v>676</v>
+      </c>
+      <c r="S66" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>113</v>
       </c>
@@ -5081,10 +6551,13 @@
         <v>20</v>
       </c>
       <c r="R67" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.4">
+        <v>677</v>
+      </c>
+      <c r="S67" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>118</v>
       </c>
@@ -5113,10 +6586,13 @@
         <v>20</v>
       </c>
       <c r="R68" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.4">
+        <v>678</v>
+      </c>
+      <c r="S68" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>122</v>
       </c>
@@ -5142,10 +6618,13 @@
         <v>20</v>
       </c>
       <c r="R69" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.4">
+        <v>679</v>
+      </c>
+      <c r="S69" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>124</v>
       </c>
@@ -5171,10 +6650,13 @@
         <v>34</v>
       </c>
       <c r="R70" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.4">
+        <v>680</v>
+      </c>
+      <c r="S70" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>125</v>
       </c>
@@ -5209,10 +6691,13 @@
         <v>73</v>
       </c>
       <c r="R71" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.4">
+        <v>661</v>
+      </c>
+      <c r="S71" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>126</v>
       </c>
@@ -5238,10 +6723,13 @@
         <v>20</v>
       </c>
       <c r="R72" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.4">
+        <v>681</v>
+      </c>
+      <c r="S72" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>127</v>
       </c>
@@ -5267,10 +6755,13 @@
         <v>20</v>
       </c>
       <c r="R73" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.4">
+        <v>682</v>
+      </c>
+      <c r="S73" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>135</v>
       </c>
@@ -5302,10 +6793,13 @@
         <v>74</v>
       </c>
       <c r="R74" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.4">
+        <v>683</v>
+      </c>
+      <c r="S74" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>138</v>
       </c>
@@ -5334,10 +6828,13 @@
         <v>20</v>
       </c>
       <c r="R75" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.4">
+        <v>684</v>
+      </c>
+      <c r="S75" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>139</v>
       </c>
@@ -5363,10 +6860,13 @@
         <v>20</v>
       </c>
       <c r="R76" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.4">
+        <v>685</v>
+      </c>
+      <c r="S76" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>140</v>
       </c>
@@ -5392,10 +6892,13 @@
         <v>34</v>
       </c>
       <c r="R77" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.4">
+        <v>686</v>
+      </c>
+      <c r="S77" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>144</v>
       </c>
@@ -5424,10 +6927,13 @@
         <v>20</v>
       </c>
       <c r="R78" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.4">
+        <v>687</v>
+      </c>
+      <c r="S78" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>145</v>
       </c>
@@ -5456,10 +6962,13 @@
         <v>20</v>
       </c>
       <c r="R79" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.4">
+        <v>688</v>
+      </c>
+      <c r="S79" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>147</v>
       </c>
@@ -5485,10 +6994,13 @@
         <v>20</v>
       </c>
       <c r="R80" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.4">
+        <v>689</v>
+      </c>
+      <c r="S80" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>148</v>
       </c>
@@ -5514,10 +7026,13 @@
         <v>34</v>
       </c>
       <c r="R81" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.4">
+        <v>690</v>
+      </c>
+      <c r="S81" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>149</v>
       </c>
@@ -5546,10 +7061,13 @@
         <v>20</v>
       </c>
       <c r="R82" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.4">
+        <v>691</v>
+      </c>
+      <c r="S82" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>154</v>
       </c>
@@ -5581,10 +7099,13 @@
         <v>74</v>
       </c>
       <c r="R83" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.4">
+        <v>692</v>
+      </c>
+      <c r="S83" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>155</v>
       </c>
@@ -5613,10 +7134,13 @@
         <v>20</v>
       </c>
       <c r="R84" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.4">
+        <v>693</v>
+      </c>
+      <c r="S84" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>157</v>
       </c>
@@ -5645,10 +7169,13 @@
         <v>20</v>
       </c>
       <c r="R85" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.4">
+        <v>694</v>
+      </c>
+      <c r="S85" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>160</v>
       </c>
@@ -5677,10 +7204,13 @@
         <v>20</v>
       </c>
       <c r="R86" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.4">
+        <v>695</v>
+      </c>
+      <c r="S86" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>162</v>
       </c>
@@ -5709,10 +7239,13 @@
         <v>34</v>
       </c>
       <c r="R87" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.4">
+        <v>696</v>
+      </c>
+      <c r="S87" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>164</v>
       </c>
@@ -5741,10 +7274,13 @@
         <v>20</v>
       </c>
       <c r="R88" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.4">
+        <v>697</v>
+      </c>
+      <c r="S88" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>165</v>
       </c>
@@ -5773,10 +7309,13 @@
         <v>20</v>
       </c>
       <c r="R89" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.4">
+        <v>698</v>
+      </c>
+      <c r="S89" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>168</v>
       </c>
@@ -5805,10 +7344,13 @@
         <v>20</v>
       </c>
       <c r="R90" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.4">
+        <v>699</v>
+      </c>
+      <c r="S90" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>170</v>
       </c>
@@ -5843,10 +7385,13 @@
         <v>91</v>
       </c>
       <c r="R91" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.4">
+        <v>700</v>
+      </c>
+      <c r="S91" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>172</v>
       </c>
@@ -5872,10 +7417,13 @@
         <v>164</v>
       </c>
       <c r="R92" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.4">
+        <v>701</v>
+      </c>
+      <c r="S92" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>174</v>
       </c>
@@ -5901,10 +7449,13 @@
         <v>20</v>
       </c>
       <c r="R93" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.4">
+        <v>702</v>
+      </c>
+      <c r="S93" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>177</v>
       </c>
@@ -5939,10 +7490,13 @@
         <v>28</v>
       </c>
       <c r="R94" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.4">
+        <v>703</v>
+      </c>
+      <c r="S94" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>177</v>
       </c>
@@ -5977,10 +7531,13 @@
         <v>28</v>
       </c>
       <c r="R95" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.4">
+        <v>704</v>
+      </c>
+      <c r="S95" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>179</v>
       </c>
@@ -6006,10 +7563,13 @@
         <v>34</v>
       </c>
       <c r="R96" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.4">
+        <v>705</v>
+      </c>
+      <c r="S96" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>180</v>
       </c>
@@ -6035,10 +7595,13 @@
         <v>20</v>
       </c>
       <c r="R97" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.4">
+        <v>706</v>
+      </c>
+      <c r="S97" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>181</v>
       </c>
@@ -6064,10 +7627,13 @@
         <v>34</v>
       </c>
       <c r="R98" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.4">
+        <v>707</v>
+      </c>
+      <c r="S98" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>182</v>
       </c>
@@ -6093,10 +7659,13 @@
         <v>20</v>
       </c>
       <c r="R99" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.4">
+        <v>708</v>
+      </c>
+      <c r="S99" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>188</v>
       </c>
@@ -6125,10 +7694,13 @@
         <v>20</v>
       </c>
       <c r="R100" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.4">
+        <v>709</v>
+      </c>
+      <c r="S100" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>190</v>
       </c>
@@ -6163,10 +7735,13 @@
         <v>28</v>
       </c>
       <c r="R101" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.4">
+        <v>710</v>
+      </c>
+      <c r="S101" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>199</v>
       </c>
@@ -6195,10 +7770,13 @@
         <v>20</v>
       </c>
       <c r="R102" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.4">
+        <v>711</v>
+      </c>
+      <c r="S102" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>200</v>
       </c>
@@ -6227,10 +7805,13 @@
         <v>20</v>
       </c>
       <c r="R103" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.4">
+        <v>712</v>
+      </c>
+      <c r="S103" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>206</v>
       </c>
@@ -6259,10 +7840,13 @@
         <v>20</v>
       </c>
       <c r="R104" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.4">
+        <v>713</v>
+      </c>
+      <c r="S104" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>207</v>
       </c>
@@ -6291,10 +7875,13 @@
         <v>20</v>
       </c>
       <c r="R105" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.4">
+        <v>714</v>
+      </c>
+      <c r="S105" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>208</v>
       </c>
@@ -6323,10 +7910,13 @@
         <v>20</v>
       </c>
       <c r="R106" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.4">
+        <v>715</v>
+      </c>
+      <c r="S106" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>209</v>
       </c>
@@ -6355,10 +7945,13 @@
         <v>20</v>
       </c>
       <c r="R107" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.4">
+        <v>716</v>
+      </c>
+      <c r="S107" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>210</v>
       </c>
@@ -6387,10 +7980,13 @@
         <v>20</v>
       </c>
       <c r="R108" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.4">
+        <v>717</v>
+      </c>
+      <c r="S108" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>211</v>
       </c>
@@ -6419,10 +8015,13 @@
         <v>20</v>
       </c>
       <c r="R109" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.4">
+        <v>718</v>
+      </c>
+      <c r="S109" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>224</v>
       </c>
@@ -6448,10 +8047,13 @@
         <v>34</v>
       </c>
       <c r="R110" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.4">
+        <v>664</v>
+      </c>
+      <c r="S110" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>235</v>
       </c>
@@ -6477,10 +8079,13 @@
         <v>20</v>
       </c>
       <c r="R111" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.4">
+        <v>719</v>
+      </c>
+      <c r="S111" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>238</v>
       </c>
@@ -6509,10 +8114,13 @@
         <v>20</v>
       </c>
       <c r="R112" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.4">
+        <v>720</v>
+      </c>
+      <c r="S112" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>240</v>
       </c>
@@ -6541,10 +8149,13 @@
         <v>20</v>
       </c>
       <c r="R113" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.4">
+        <v>721</v>
+      </c>
+      <c r="S113" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>251</v>
       </c>
@@ -6570,10 +8181,13 @@
         <v>20</v>
       </c>
       <c r="R114" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.4">
+        <v>722</v>
+      </c>
+      <c r="S114" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>252</v>
       </c>
@@ -6599,10 +8213,13 @@
         <v>20</v>
       </c>
       <c r="R115" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.4">
+        <v>723</v>
+      </c>
+      <c r="S115" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>262</v>
       </c>
@@ -6631,10 +8248,13 @@
         <v>193</v>
       </c>
       <c r="R116" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.4">
+        <v>724</v>
+      </c>
+      <c r="S116" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>265</v>
       </c>
@@ -6660,10 +8280,13 @@
         <v>20</v>
       </c>
       <c r="R117" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.4">
+        <v>725</v>
+      </c>
+      <c r="S117" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>266</v>
       </c>
@@ -6695,10 +8318,13 @@
         <v>42</v>
       </c>
       <c r="R118" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.4">
+        <v>726</v>
+      </c>
+      <c r="S118" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>267</v>
       </c>
@@ -6730,10 +8356,13 @@
         <v>21</v>
       </c>
       <c r="R119" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.4">
+        <v>727</v>
+      </c>
+      <c r="S119" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>268</v>
       </c>
@@ -6759,10 +8388,13 @@
         <v>20</v>
       </c>
       <c r="R120" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.4">
+        <v>612</v>
+      </c>
+      <c r="S120" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>270</v>
       </c>
@@ -6791,10 +8423,13 @@
         <v>20</v>
       </c>
       <c r="R121" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.4">
+        <v>728</v>
+      </c>
+      <c r="S121" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>272</v>
       </c>
@@ -6820,10 +8455,13 @@
         <v>20</v>
       </c>
       <c r="R122" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.4">
+        <v>729</v>
+      </c>
+      <c r="S122" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>273</v>
       </c>
@@ -6849,10 +8487,13 @@
         <v>20</v>
       </c>
       <c r="R123" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.4">
+        <v>730</v>
+      </c>
+      <c r="S123" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>274</v>
       </c>
@@ -6887,10 +8528,13 @@
         <v>28</v>
       </c>
       <c r="R124" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.4">
+        <v>731</v>
+      </c>
+      <c r="S124" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>275</v>
       </c>
@@ -6916,10 +8560,13 @@
         <v>20</v>
       </c>
       <c r="R125" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.4">
+        <v>732</v>
+      </c>
+      <c r="S125" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>279</v>
       </c>
@@ -6945,10 +8592,13 @@
         <v>20</v>
       </c>
       <c r="R126" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.4">
+        <v>733</v>
+      </c>
+      <c r="S126" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>281</v>
       </c>
@@ -6974,10 +8624,13 @@
         <v>34</v>
       </c>
       <c r="R127" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.4">
+        <v>734</v>
+      </c>
+      <c r="S127" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>283</v>
       </c>
@@ -7009,10 +8662,13 @@
         <v>21</v>
       </c>
       <c r="R128" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.4">
+        <v>735</v>
+      </c>
+      <c r="S128" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>285</v>
       </c>
@@ -7044,10 +8700,13 @@
         <v>91</v>
       </c>
       <c r="R129" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.4">
+        <v>736</v>
+      </c>
+      <c r="S129" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>288</v>
       </c>
@@ -7079,10 +8738,13 @@
         <v>42</v>
       </c>
       <c r="R130" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.4">
+        <v>737</v>
+      </c>
+      <c r="S130" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>290</v>
       </c>
@@ -7111,10 +8773,13 @@
         <v>20</v>
       </c>
       <c r="R131" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.4">
+        <v>738</v>
+      </c>
+      <c r="S131" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>292</v>
       </c>
@@ -7146,10 +8811,13 @@
         <v>28</v>
       </c>
       <c r="R132" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.4">
+        <v>739</v>
+      </c>
+      <c r="S132" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>293</v>
       </c>
@@ -7178,10 +8846,13 @@
         <v>20</v>
       </c>
       <c r="R133" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.4">
+        <v>740</v>
+      </c>
+      <c r="S133" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>294</v>
       </c>
@@ -7210,10 +8881,13 @@
         <v>20</v>
       </c>
       <c r="R134" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.4">
+        <v>741</v>
+      </c>
+      <c r="S134" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>295</v>
       </c>
@@ -7242,10 +8916,13 @@
         <v>20</v>
       </c>
       <c r="R135" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.4">
+        <v>742</v>
+      </c>
+      <c r="S135" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>296</v>
       </c>
@@ -7274,10 +8951,13 @@
         <v>20</v>
       </c>
       <c r="R136" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.4">
+        <v>743</v>
+      </c>
+      <c r="S136" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>297</v>
       </c>
@@ -7306,10 +8986,13 @@
         <v>34</v>
       </c>
       <c r="R137" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.4">
+        <v>744</v>
+      </c>
+      <c r="S137" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>299</v>
       </c>
@@ -7338,10 +9021,13 @@
         <v>20</v>
       </c>
       <c r="R138" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.4">
+        <v>745</v>
+      </c>
+      <c r="S138" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>300</v>
       </c>
@@ -7370,10 +9056,13 @@
         <v>20</v>
       </c>
       <c r="R139" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.4">
+        <v>746</v>
+      </c>
+      <c r="S139" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>301</v>
       </c>
@@ -7402,10 +9091,13 @@
         <v>20</v>
       </c>
       <c r="R140" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.4">
+        <v>747</v>
+      </c>
+      <c r="S140" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>302</v>
       </c>
@@ -7434,10 +9126,13 @@
         <v>20</v>
       </c>
       <c r="R141" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.4">
+        <v>748</v>
+      </c>
+      <c r="S141" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>307</v>
       </c>
@@ -7472,10 +9167,13 @@
         <v>42</v>
       </c>
       <c r="R142" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.4">
+        <v>749</v>
+      </c>
+      <c r="S142" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>308</v>
       </c>
@@ -7507,10 +9205,13 @@
         <v>42</v>
       </c>
       <c r="R143" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.4">
+        <v>750</v>
+      </c>
+      <c r="S143" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>314</v>
       </c>
@@ -7539,10 +9240,13 @@
         <v>20</v>
       </c>
       <c r="R144" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.4">
+        <v>751</v>
+      </c>
+      <c r="S144" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>317</v>
       </c>
@@ -7571,10 +9275,13 @@
         <v>20</v>
       </c>
       <c r="R145" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.4">
+        <v>752</v>
+      </c>
+      <c r="S145" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>318</v>
       </c>
@@ -7603,10 +9310,13 @@
         <v>20</v>
       </c>
       <c r="R146" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.4">
+        <v>753</v>
+      </c>
+      <c r="S146" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>338</v>
       </c>
@@ -7632,10 +9342,13 @@
         <v>20</v>
       </c>
       <c r="R147" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.4">
+        <v>754</v>
+      </c>
+      <c r="S147" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>342</v>
       </c>
@@ -7661,10 +9374,13 @@
         <v>20</v>
       </c>
       <c r="R148" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.4">
+        <v>755</v>
+      </c>
+      <c r="S148" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>357</v>
       </c>
@@ -7693,10 +9409,13 @@
         <v>20</v>
       </c>
       <c r="R149" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.4">
+        <v>756</v>
+      </c>
+      <c r="S149" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>359</v>
       </c>
@@ -7728,10 +9447,13 @@
         <v>29</v>
       </c>
       <c r="R150" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.4">
+        <v>757</v>
+      </c>
+      <c r="S150" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>361</v>
       </c>
@@ -7763,10 +9485,13 @@
         <v>193</v>
       </c>
       <c r="R151" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.4">
+        <v>758</v>
+      </c>
+      <c r="S151" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>365</v>
       </c>
@@ -7795,10 +9520,13 @@
         <v>20</v>
       </c>
       <c r="R152" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.4">
+        <v>759</v>
+      </c>
+      <c r="S152" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>371</v>
       </c>
@@ -7824,10 +9552,13 @@
         <v>20</v>
       </c>
       <c r="R153" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.4">
+        <v>760</v>
+      </c>
+      <c r="S153" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>373</v>
       </c>
@@ -7856,10 +9587,13 @@
         <v>20</v>
       </c>
       <c r="R154" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.4">
+        <v>761</v>
+      </c>
+      <c r="S154" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>375</v>
       </c>
@@ -7891,10 +9625,13 @@
         <v>247</v>
       </c>
       <c r="R155" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.4">
+        <v>762</v>
+      </c>
+      <c r="S155" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>376</v>
       </c>
@@ -7923,10 +9660,13 @@
         <v>20</v>
       </c>
       <c r="R156" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.4">
+        <v>763</v>
+      </c>
+      <c r="S156" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>377</v>
       </c>
@@ -7952,10 +9692,13 @@
         <v>20</v>
       </c>
       <c r="R157" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.4">
+        <v>764</v>
+      </c>
+      <c r="S157" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>378</v>
       </c>
@@ -7981,10 +9724,13 @@
         <v>20</v>
       </c>
       <c r="R158" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.4">
+        <v>765</v>
+      </c>
+      <c r="S158" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>379</v>
       </c>
@@ -8013,10 +9759,13 @@
         <v>20</v>
       </c>
       <c r="R159" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.4">
+        <v>766</v>
+      </c>
+      <c r="S159" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>384</v>
       </c>
@@ -8048,10 +9797,13 @@
         <v>247</v>
       </c>
       <c r="R160" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.4">
+        <v>767</v>
+      </c>
+      <c r="S160" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>385</v>
       </c>
@@ -8083,10 +9835,13 @@
         <v>43</v>
       </c>
       <c r="R161" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.4">
+        <v>768</v>
+      </c>
+      <c r="S161" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>386</v>
       </c>
@@ -8115,10 +9870,13 @@
         <v>20</v>
       </c>
       <c r="R162" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.4">
+        <v>769</v>
+      </c>
+      <c r="S162" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>387</v>
       </c>
@@ -8144,10 +9902,13 @@
         <v>20</v>
       </c>
       <c r="R163" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.4">
+        <v>770</v>
+      </c>
+      <c r="S163" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>389</v>
       </c>
@@ -8179,10 +9940,13 @@
         <v>42</v>
       </c>
       <c r="R164" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.4">
+        <v>771</v>
+      </c>
+      <c r="S164" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>392</v>
       </c>
@@ -8211,10 +9975,13 @@
         <v>21</v>
       </c>
       <c r="R165" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.4">
+        <v>772</v>
+      </c>
+      <c r="S165" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>396</v>
       </c>
@@ -8243,10 +10010,13 @@
         <v>20</v>
       </c>
       <c r="R166" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.4">
+        <v>773</v>
+      </c>
+      <c r="S166" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>399</v>
       </c>
@@ -8272,10 +10042,13 @@
         <v>20</v>
       </c>
       <c r="R167" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.4">
+        <v>774</v>
+      </c>
+      <c r="S167" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>400</v>
       </c>
@@ -8301,10 +10074,13 @@
         <v>20</v>
       </c>
       <c r="R168" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.4">
+        <v>775</v>
+      </c>
+      <c r="S168" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>401</v>
       </c>
@@ -8330,10 +10106,13 @@
         <v>20</v>
       </c>
       <c r="R169" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.4">
+        <v>776</v>
+      </c>
+      <c r="S169" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>404</v>
       </c>
@@ -8359,10 +10138,13 @@
         <v>20</v>
       </c>
       <c r="R170" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.4">
+        <v>776</v>
+      </c>
+      <c r="S170" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>405</v>
       </c>
@@ -8388,10 +10170,13 @@
         <v>20</v>
       </c>
       <c r="R171" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.4">
+        <v>777</v>
+      </c>
+      <c r="S171" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>406</v>
       </c>
@@ -8420,10 +10205,13 @@
         <v>28</v>
       </c>
       <c r="R172" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.4">
+        <v>778</v>
+      </c>
+      <c r="S172" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>410</v>
       </c>
@@ -8452,10 +10240,13 @@
         <v>20</v>
       </c>
       <c r="R173" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.4">
+        <v>779</v>
+      </c>
+      <c r="S173" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>411</v>
       </c>
@@ -8484,10 +10275,13 @@
         <v>20</v>
       </c>
       <c r="R174" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.4">
+        <v>780</v>
+      </c>
+      <c r="S174" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>413</v>
       </c>
@@ -8513,10 +10307,13 @@
         <v>20</v>
       </c>
       <c r="R175" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.4">
+        <v>781</v>
+      </c>
+      <c r="S175" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>413</v>
       </c>
@@ -8542,10 +10339,13 @@
         <v>20</v>
       </c>
       <c r="R176" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.4">
+        <v>782</v>
+      </c>
+      <c r="S176" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>413</v>
       </c>
@@ -8571,10 +10371,13 @@
         <v>20</v>
       </c>
       <c r="R177" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.4">
+        <v>783</v>
+      </c>
+      <c r="S177" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>426</v>
       </c>
@@ -8603,10 +10406,13 @@
         <v>20</v>
       </c>
       <c r="R178" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.4">
+        <v>784</v>
+      </c>
+      <c r="S178" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>427</v>
       </c>
@@ -8632,10 +10438,13 @@
         <v>20</v>
       </c>
       <c r="R179" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.4">
+        <v>785</v>
+      </c>
+      <c r="S179" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>428</v>
       </c>
@@ -8664,10 +10473,13 @@
         <v>73</v>
       </c>
       <c r="R180" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.4">
+        <v>786</v>
+      </c>
+      <c r="S180" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>431</v>
       </c>
@@ -8699,10 +10511,13 @@
         <v>91</v>
       </c>
       <c r="R181" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.4">
+        <v>787</v>
+      </c>
+      <c r="S181" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>437</v>
       </c>
@@ -8728,10 +10543,13 @@
         <v>20</v>
       </c>
       <c r="R182" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.4">
+        <v>788</v>
+      </c>
+      <c r="S182" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>445</v>
       </c>
@@ -8766,10 +10584,13 @@
         <v>193</v>
       </c>
       <c r="R183" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.4">
+        <v>789</v>
+      </c>
+      <c r="S183" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>446</v>
       </c>
@@ -8798,10 +10619,13 @@
         <v>21</v>
       </c>
       <c r="R184" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.4">
+        <v>790</v>
+      </c>
+      <c r="S184" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>447</v>
       </c>
@@ -8827,10 +10651,13 @@
         <v>20</v>
       </c>
       <c r="R185" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.4">
+        <v>791</v>
+      </c>
+      <c r="S185" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>462</v>
       </c>
@@ -8856,10 +10683,13 @@
         <v>34</v>
       </c>
       <c r="R186" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.4">
+        <v>792</v>
+      </c>
+      <c r="S186" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>463</v>
       </c>
@@ -8885,10 +10715,13 @@
         <v>20</v>
       </c>
       <c r="R187" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.4">
+        <v>793</v>
+      </c>
+      <c r="S187" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A188">
         <v>472</v>
       </c>
@@ -8914,10 +10747,13 @@
         <v>20</v>
       </c>
       <c r="R188" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.4">
+        <v>750</v>
+      </c>
+      <c r="S188" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A189">
         <v>473</v>
       </c>
@@ -8943,10 +10779,13 @@
         <v>34</v>
       </c>
       <c r="R189" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.4">
+        <v>794</v>
+      </c>
+      <c r="S189" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A190">
         <v>475</v>
       </c>
@@ -8975,10 +10814,13 @@
         <v>20</v>
       </c>
       <c r="R190" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.4">
+        <v>795</v>
+      </c>
+      <c r="S190" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A191">
         <v>477</v>
       </c>
@@ -9028,10 +10870,13 @@
         <v>42</v>
       </c>
       <c r="R191" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.4">
+        <v>796</v>
+      </c>
+      <c r="S191" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A192">
         <v>480</v>
       </c>
@@ -9057,10 +10902,13 @@
         <v>20</v>
       </c>
       <c r="R192" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.4">
+        <v>797</v>
+      </c>
+      <c r="S192" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A193">
         <v>483</v>
       </c>
@@ -9086,10 +10934,13 @@
         <v>20</v>
       </c>
       <c r="R193" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.4">
+        <v>798</v>
+      </c>
+      <c r="S193" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A194">
         <v>484</v>
       </c>
@@ -9115,10 +10966,13 @@
         <v>20</v>
       </c>
       <c r="R194" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.4">
+        <v>799</v>
+      </c>
+      <c r="S194" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A195">
         <v>494</v>
       </c>
@@ -9147,10 +11001,13 @@
         <v>34</v>
       </c>
       <c r="R195" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.4">
+        <v>800</v>
+      </c>
+      <c r="S195" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A196">
         <v>495</v>
       </c>
@@ -9179,10 +11036,13 @@
         <v>20</v>
       </c>
       <c r="R196" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.4">
+        <v>801</v>
+      </c>
+      <c r="S196" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A197">
         <v>496</v>
       </c>
@@ -9208,10 +11068,13 @@
         <v>20</v>
       </c>
       <c r="R197" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.4">
+        <v>802</v>
+      </c>
+      <c r="S197" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A198">
         <v>504</v>
       </c>
@@ -9243,10 +11106,13 @@
         <v>41</v>
       </c>
       <c r="R198" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.4">
+        <v>803</v>
+      </c>
+      <c r="S198" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A199">
         <v>505</v>
       </c>
@@ -9278,10 +11144,13 @@
         <v>91</v>
       </c>
       <c r="R199" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.4">
+        <v>804</v>
+      </c>
+      <c r="S199" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A200">
         <v>509</v>
       </c>
@@ -9307,10 +11176,13 @@
         <v>34</v>
       </c>
       <c r="R200" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.4">
+        <v>805</v>
+      </c>
+      <c r="S200" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A201">
         <v>510</v>
       </c>
@@ -9342,10 +11214,13 @@
         <v>73</v>
       </c>
       <c r="R201" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.4">
+        <v>806</v>
+      </c>
+      <c r="S201" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A202">
         <v>511</v>
       </c>
@@ -9373,8 +11248,11 @@
       <c r="J202" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R202" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A203">
         <v>511</v>
       </c>
@@ -9403,10 +11281,13 @@
         <v>28</v>
       </c>
       <c r="R203" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.4">
+        <v>808</v>
+      </c>
+      <c r="S203" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A204">
         <v>512</v>
       </c>
@@ -9432,10 +11313,13 @@
         <v>20</v>
       </c>
       <c r="R204" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.4">
+        <v>809</v>
+      </c>
+      <c r="S204" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A205">
         <v>513</v>
       </c>
@@ -9464,10 +11348,13 @@
         <v>20</v>
       </c>
       <c r="R205" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.4">
+        <v>810</v>
+      </c>
+      <c r="S205" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A206">
         <v>514</v>
       </c>
@@ -9493,10 +11380,13 @@
         <v>20</v>
       </c>
       <c r="R206" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.4">
+        <v>811</v>
+      </c>
+      <c r="S206" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A207">
         <v>515</v>
       </c>
@@ -9525,10 +11415,13 @@
         <v>21</v>
       </c>
       <c r="R207" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.4">
+        <v>812</v>
+      </c>
+      <c r="S207" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A208">
         <v>516</v>
       </c>
@@ -9554,10 +11447,13 @@
         <v>20</v>
       </c>
       <c r="R208" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.4">
+        <v>813</v>
+      </c>
+      <c r="S208" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A209">
         <v>517</v>
       </c>
@@ -9583,10 +11479,13 @@
         <v>20</v>
       </c>
       <c r="R209" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.4">
+        <v>814</v>
+      </c>
+      <c r="S209" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A210">
         <v>518</v>
       </c>
@@ -9618,10 +11517,13 @@
         <v>247</v>
       </c>
       <c r="R210" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.4">
+        <v>815</v>
+      </c>
+      <c r="S210" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A211">
         <v>520</v>
       </c>
@@ -9650,10 +11552,13 @@
         <v>41</v>
       </c>
       <c r="R211" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.4">
+        <v>816</v>
+      </c>
+      <c r="S211" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A212">
         <v>523</v>
       </c>
@@ -9685,10 +11590,13 @@
         <v>247</v>
       </c>
       <c r="R212" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.4">
+        <v>817</v>
+      </c>
+      <c r="S212" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A213">
         <v>530</v>
       </c>
@@ -9717,10 +11625,13 @@
         <v>20</v>
       </c>
       <c r="R213" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.4">
+        <v>818</v>
+      </c>
+      <c r="S213" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A214">
         <v>531</v>
       </c>
@@ -9746,10 +11657,13 @@
         <v>20</v>
       </c>
       <c r="R214" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.4">
+        <v>819</v>
+      </c>
+      <c r="S214" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A215">
         <v>533</v>
       </c>
@@ -9778,10 +11692,13 @@
         <v>20</v>
       </c>
       <c r="R215" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.4">
+        <v>820</v>
+      </c>
+      <c r="S215" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A216">
         <v>537</v>
       </c>
@@ -9807,10 +11724,13 @@
         <v>20</v>
       </c>
       <c r="R216" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.4">
+        <v>821</v>
+      </c>
+      <c r="S216" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A217">
         <v>538</v>
       </c>
@@ -9836,10 +11756,13 @@
         <v>20</v>
       </c>
       <c r="R217" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.4">
+        <v>822</v>
+      </c>
+      <c r="S217" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A218">
         <v>541</v>
       </c>
@@ -9868,10 +11791,13 @@
         <v>20</v>
       </c>
       <c r="R218" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.4">
+        <v>823</v>
+      </c>
+      <c r="S218" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A219">
         <v>543</v>
       </c>
@@ -9900,10 +11826,13 @@
         <v>34</v>
       </c>
       <c r="R219" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.4">
+        <v>824</v>
+      </c>
+      <c r="S219" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A220">
         <v>557</v>
       </c>
@@ -9935,10 +11864,13 @@
         <v>247</v>
       </c>
       <c r="R220" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.4">
+        <v>825</v>
+      </c>
+      <c r="S220" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A221">
         <v>558</v>
       </c>
@@ -9973,10 +11905,13 @@
         <v>247</v>
       </c>
       <c r="R221" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.4">
+        <v>826</v>
+      </c>
+      <c r="S221" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A222">
         <v>559</v>
       </c>
@@ -10008,10 +11943,13 @@
         <v>43</v>
       </c>
       <c r="R222" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.4">
+        <v>827</v>
+      </c>
+      <c r="S222" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A223">
         <v>564</v>
       </c>
@@ -10040,10 +11978,13 @@
         <v>20</v>
       </c>
       <c r="R223" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.4">
+        <v>828</v>
+      </c>
+      <c r="S223" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A224">
         <v>567</v>
       </c>
@@ -10069,10 +12010,13 @@
         <v>20</v>
       </c>
       <c r="R224" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.4">
+        <v>829</v>
+      </c>
+      <c r="S224" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A225">
         <v>571</v>
       </c>
@@ -10098,10 +12042,13 @@
         <v>20</v>
       </c>
       <c r="R225" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.4">
+        <v>830</v>
+      </c>
+      <c r="S225" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A226">
         <v>574</v>
       </c>
@@ -10127,10 +12074,13 @@
         <v>76</v>
       </c>
       <c r="R226" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.4">
+        <v>831</v>
+      </c>
+      <c r="S226" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A227">
         <v>575</v>
       </c>
@@ -10156,10 +12106,13 @@
         <v>20</v>
       </c>
       <c r="R227" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.4">
+        <v>832</v>
+      </c>
+      <c r="S227" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A228">
         <v>577</v>
       </c>
@@ -10185,10 +12138,13 @@
         <v>76</v>
       </c>
       <c r="R228" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.4">
+        <v>833</v>
+      </c>
+      <c r="S228" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A229">
         <v>579</v>
       </c>
@@ -10214,10 +12170,13 @@
         <v>76</v>
       </c>
       <c r="R229" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.4">
+        <v>834</v>
+      </c>
+      <c r="S229" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A230">
         <v>580</v>
       </c>
@@ -10243,10 +12202,13 @@
         <v>20</v>
       </c>
       <c r="R230" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.4">
+        <v>835</v>
+      </c>
+      <c r="S230" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A231">
         <v>581</v>
       </c>
@@ -10272,10 +12234,13 @@
         <v>76</v>
       </c>
       <c r="R231" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.4">
+        <v>836</v>
+      </c>
+      <c r="S231" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A232">
         <v>582</v>
       </c>
@@ -10301,10 +12266,13 @@
         <v>34</v>
       </c>
       <c r="R232" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.4">
+        <v>837</v>
+      </c>
+      <c r="S232" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A233">
         <v>583</v>
       </c>
@@ -10330,10 +12298,13 @@
         <v>76</v>
       </c>
       <c r="R233" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.4">
+        <v>838</v>
+      </c>
+      <c r="S233" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A234">
         <v>588</v>
       </c>
@@ -10359,10 +12330,13 @@
         <v>164</v>
       </c>
       <c r="R234" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.4">
+        <v>839</v>
+      </c>
+      <c r="S234" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A235">
         <v>589</v>
       </c>
@@ -10391,10 +12365,13 @@
         <v>164</v>
       </c>
       <c r="R235" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.4">
+        <v>840</v>
+      </c>
+      <c r="S235" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A236">
         <v>591</v>
       </c>
@@ -10420,10 +12397,13 @@
         <v>20</v>
       </c>
       <c r="R236" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.4">
+        <v>841</v>
+      </c>
+      <c r="S236" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A237">
         <v>595</v>
       </c>
@@ -10449,10 +12429,13 @@
         <v>20</v>
       </c>
       <c r="R237" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.4">
+        <v>842</v>
+      </c>
+      <c r="S237" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A238">
         <v>600</v>
       </c>
@@ -10478,10 +12461,13 @@
         <v>20</v>
       </c>
       <c r="R238" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.4">
+        <v>843</v>
+      </c>
+      <c r="S238" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A239">
         <v>606</v>
       </c>
@@ -10507,10 +12493,13 @@
         <v>20</v>
       </c>
       <c r="R239" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.4">
+        <v>844</v>
+      </c>
+      <c r="S239" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A240">
         <v>614</v>
       </c>
@@ -10542,10 +12531,13 @@
         <v>42</v>
       </c>
       <c r="R240" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.4">
+        <v>845</v>
+      </c>
+      <c r="S240" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A241">
         <v>627</v>
       </c>
@@ -10571,10 +12563,13 @@
         <v>20</v>
       </c>
       <c r="R241" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.4">
+        <v>846</v>
+      </c>
+      <c r="S241" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A242">
         <v>648</v>
       </c>
@@ -10600,10 +12595,13 @@
         <v>20</v>
       </c>
       <c r="R242" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.4">
+        <v>847</v>
+      </c>
+      <c r="S242" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A243">
         <v>649</v>
       </c>
@@ -10629,10 +12627,13 @@
         <v>20</v>
       </c>
       <c r="R243" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.4">
+        <v>848</v>
+      </c>
+      <c r="S243" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A244">
         <v>650</v>
       </c>
@@ -10658,10 +12659,13 @@
         <v>34</v>
       </c>
       <c r="R244" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.4">
+        <v>849</v>
+      </c>
+      <c r="S244" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A245">
         <v>651</v>
       </c>
@@ -10687,10 +12691,13 @@
         <v>20</v>
       </c>
       <c r="R245" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.4">
+        <v>850</v>
+      </c>
+      <c r="S245" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A246">
         <v>655</v>
       </c>
@@ -10716,10 +12723,13 @@
         <v>20</v>
       </c>
       <c r="R246" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.4">
+        <v>851</v>
+      </c>
+      <c r="S246" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A247">
         <v>656</v>
       </c>
@@ -10748,10 +12758,13 @@
         <v>34</v>
       </c>
       <c r="R247" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.4">
+        <v>852</v>
+      </c>
+      <c r="S247" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A248">
         <v>659</v>
       </c>
@@ -10786,10 +12799,13 @@
         <v>28</v>
       </c>
       <c r="R248" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.4">
+        <v>853</v>
+      </c>
+      <c r="S248" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A249">
         <v>659</v>
       </c>
@@ -10824,10 +12840,13 @@
         <v>28</v>
       </c>
       <c r="R249" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.4">
+        <v>854</v>
+      </c>
+      <c r="S249" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A250">
         <v>660</v>
       </c>
@@ -10856,10 +12875,13 @@
         <v>20</v>
       </c>
       <c r="R250" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.4">
+        <v>855</v>
+      </c>
+      <c r="S250" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A251">
         <v>661</v>
       </c>
@@ -10888,10 +12910,13 @@
         <v>20</v>
       </c>
       <c r="R251" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.4">
+        <v>856</v>
+      </c>
+      <c r="S251" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A252">
         <v>664</v>
       </c>
@@ -10923,10 +12948,13 @@
         <v>74</v>
       </c>
       <c r="R252" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.4">
+        <v>857</v>
+      </c>
+      <c r="S252" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A253">
         <v>680</v>
       </c>
@@ -10952,10 +12980,13 @@
         <v>20</v>
       </c>
       <c r="R253" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.4">
+        <v>858</v>
+      </c>
+      <c r="S253" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A254">
         <v>681</v>
       </c>
@@ -10981,10 +13012,13 @@
         <v>34</v>
       </c>
       <c r="R254" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.4">
+        <v>859</v>
+      </c>
+      <c r="S254" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A255">
         <v>682</v>
       </c>
@@ -11010,10 +13044,13 @@
         <v>20</v>
       </c>
       <c r="R255" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.4">
+        <v>860</v>
+      </c>
+      <c r="S255" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A256">
         <v>683</v>
       </c>
@@ -11039,10 +13076,13 @@
         <v>20</v>
       </c>
       <c r="R256" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.4">
+        <v>861</v>
+      </c>
+      <c r="S256" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A257">
         <v>684</v>
       </c>
@@ -11068,10 +13108,13 @@
         <v>20</v>
       </c>
       <c r="R257" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.4">
+        <v>862</v>
+      </c>
+      <c r="S257" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A258">
         <v>685</v>
       </c>
@@ -11097,10 +13140,13 @@
         <v>20</v>
       </c>
       <c r="R258" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.4">
+        <v>863</v>
+      </c>
+      <c r="S258" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A259">
         <v>686</v>
       </c>
@@ -11126,10 +13172,13 @@
         <v>34</v>
       </c>
       <c r="R259" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.4">
+        <v>864</v>
+      </c>
+      <c r="S259" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A260">
         <v>687</v>
       </c>
@@ -11155,10 +13204,13 @@
         <v>20</v>
       </c>
       <c r="R260" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.4">
+        <v>865</v>
+      </c>
+      <c r="S260" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A261">
         <v>691</v>
       </c>
@@ -11187,10 +13239,13 @@
         <v>42</v>
       </c>
       <c r="R261" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.4">
+        <v>866</v>
+      </c>
+      <c r="S261" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A262">
         <v>692</v>
       </c>
@@ -11219,10 +13274,13 @@
         <v>41</v>
       </c>
       <c r="R262" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.4">
+        <v>620</v>
+      </c>
+      <c r="S262" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A263">
         <v>694</v>
       </c>
@@ -11254,10 +13312,13 @@
         <v>377</v>
       </c>
       <c r="R263" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.4">
+        <v>867</v>
+      </c>
+      <c r="S263" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A264">
         <v>715</v>
       </c>
@@ -11298,10 +13359,13 @@
         <v>28</v>
       </c>
       <c r="R264" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.4">
+        <v>868</v>
+      </c>
+      <c r="S264" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A265">
         <v>716</v>
       </c>
@@ -11345,10 +13409,13 @@
         <v>28</v>
       </c>
       <c r="R265" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.4">
+        <v>869</v>
+      </c>
+      <c r="S265" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A266">
         <v>717</v>
       </c>
@@ -11389,10 +13456,13 @@
         <v>28</v>
       </c>
       <c r="R266" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.4">
+        <v>870</v>
+      </c>
+      <c r="S266" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A267">
         <v>722</v>
       </c>
@@ -11421,10 +13491,13 @@
         <v>20</v>
       </c>
       <c r="R267" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.4">
+        <v>846</v>
+      </c>
+      <c r="S267" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A268">
         <v>723</v>
       </c>
@@ -11453,10 +13526,13 @@
         <v>34</v>
       </c>
       <c r="R268" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.4">
+        <v>871</v>
+      </c>
+      <c r="S268" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A269">
         <v>725</v>
       </c>
@@ -11485,10 +13561,13 @@
         <v>20</v>
       </c>
       <c r="R269" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.4">
+        <v>872</v>
+      </c>
+      <c r="S269" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A270">
         <v>726</v>
       </c>
@@ -11517,10 +13596,13 @@
         <v>20</v>
       </c>
       <c r="R270" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.4">
+        <v>873</v>
+      </c>
+      <c r="S270" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A271">
         <v>727</v>
       </c>
@@ -11549,10 +13631,13 @@
         <v>20</v>
       </c>
       <c r="R271" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.4">
+        <v>874</v>
+      </c>
+      <c r="S271" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A272">
         <v>728</v>
       </c>
@@ -11581,10 +13666,13 @@
         <v>20</v>
       </c>
       <c r="R272" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.4">
+        <v>875</v>
+      </c>
+      <c r="S272" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A273">
         <v>729</v>
       </c>
@@ -11613,10 +13701,13 @@
         <v>20</v>
       </c>
       <c r="R273" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.4">
+        <v>876</v>
+      </c>
+      <c r="S273" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A274">
         <v>731</v>
       </c>
@@ -11654,10 +13745,13 @@
         <v>73</v>
       </c>
       <c r="R274" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.4">
+        <v>877</v>
+      </c>
+      <c r="S274" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A275">
         <v>734</v>
       </c>
@@ -11686,10 +13780,13 @@
         <v>20</v>
       </c>
       <c r="R275" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.4">
+        <v>878</v>
+      </c>
+      <c r="S275" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A276">
         <v>735</v>
       </c>
@@ -11718,10 +13815,13 @@
         <v>20</v>
       </c>
       <c r="R276" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.4">
+        <v>879</v>
+      </c>
+      <c r="S276" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A277">
         <v>736</v>
       </c>
@@ -11759,10 +13859,13 @@
         <v>28</v>
       </c>
       <c r="R277" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.4">
+        <v>880</v>
+      </c>
+      <c r="S277" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A278">
         <v>737</v>
       </c>
@@ -11788,10 +13891,13 @@
         <v>20</v>
       </c>
       <c r="R278" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.4">
+        <v>881</v>
+      </c>
+      <c r="S278" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A279">
         <v>738</v>
       </c>
@@ -11820,10 +13926,13 @@
         <v>20</v>
       </c>
       <c r="R279" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.4">
+        <v>882</v>
+      </c>
+      <c r="S279" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A280">
         <v>740</v>
       </c>
@@ -11855,10 +13964,13 @@
         <v>41</v>
       </c>
       <c r="R280" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.4">
+        <v>883</v>
+      </c>
+      <c r="S280" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A281">
         <v>742</v>
       </c>
@@ -11887,10 +13999,13 @@
         <v>20</v>
       </c>
       <c r="R281" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.4">
+        <v>884</v>
+      </c>
+      <c r="S281" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A282">
         <v>744</v>
       </c>
@@ -11928,10 +14043,13 @@
         <v>91</v>
       </c>
       <c r="R282" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.4">
+        <v>885</v>
+      </c>
+      <c r="S282" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A283">
         <v>747</v>
       </c>
@@ -11963,10 +14081,13 @@
         <v>28</v>
       </c>
       <c r="R283" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.4">
+        <v>886</v>
+      </c>
+      <c r="S283" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A284">
         <v>748</v>
       </c>
@@ -11995,10 +14116,13 @@
         <v>20</v>
       </c>
       <c r="R284" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.4">
+        <v>887</v>
+      </c>
+      <c r="S284" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A285">
         <v>764</v>
       </c>
@@ -12024,10 +14148,13 @@
         <v>20</v>
       </c>
       <c r="R285" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.4">
+        <v>888</v>
+      </c>
+      <c r="S285" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A286">
         <v>765</v>
       </c>
@@ -12053,10 +14180,13 @@
         <v>20</v>
       </c>
       <c r="R286" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.4">
+        <v>889</v>
+      </c>
+      <c r="S286" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A287">
         <v>767</v>
       </c>
@@ -12085,10 +14215,13 @@
         <v>21</v>
       </c>
       <c r="R287" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.4">
+        <v>890</v>
+      </c>
+      <c r="S287" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A288">
         <v>781</v>
       </c>
@@ -12113,8 +14246,11 @@
       <c r="I288" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R288" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A289">
         <v>783</v>
       </c>
@@ -12140,10 +14276,13 @@
         <v>20</v>
       </c>
       <c r="R289" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.4">
+        <v>892</v>
+      </c>
+      <c r="S289" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A290">
         <v>786</v>
       </c>
@@ -12169,10 +14308,13 @@
         <v>34</v>
       </c>
       <c r="R290" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.4">
+        <v>893</v>
+      </c>
+      <c r="S290" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A291">
         <v>796</v>
       </c>
@@ -12201,10 +14343,13 @@
         <v>247</v>
       </c>
       <c r="R291" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.4">
+        <v>894</v>
+      </c>
+      <c r="S291" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A292">
         <v>797</v>
       </c>
@@ -12230,10 +14375,13 @@
         <v>20</v>
       </c>
       <c r="R292" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.4">
+        <v>895</v>
+      </c>
+      <c r="S292" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A293">
         <v>798</v>
       </c>
@@ -12262,10 +14410,13 @@
         <v>377</v>
       </c>
       <c r="R293" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.4">
+        <v>896</v>
+      </c>
+      <c r="S293" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A294">
         <v>799</v>
       </c>
@@ -12294,10 +14445,13 @@
         <v>377</v>
       </c>
       <c r="R294" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.4">
+        <v>897</v>
+      </c>
+      <c r="S294" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A295">
         <v>803</v>
       </c>
@@ -12326,10 +14480,13 @@
         <v>76</v>
       </c>
       <c r="R295" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.4">
+        <v>898</v>
+      </c>
+      <c r="S295" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A296">
         <v>804</v>
       </c>
@@ -12355,10 +14512,13 @@
         <v>20</v>
       </c>
       <c r="R296" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.4">
+        <v>899</v>
+      </c>
+      <c r="S296" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A297">
         <v>805</v>
       </c>
@@ -12390,10 +14550,13 @@
         <v>74</v>
       </c>
       <c r="R297" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.4">
+        <v>900</v>
+      </c>
+      <c r="S297" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A298">
         <v>810</v>
       </c>
@@ -12431,10 +14594,13 @@
         <v>247</v>
       </c>
       <c r="R298" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.4">
+        <v>901</v>
+      </c>
+      <c r="S298" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A299">
         <v>810</v>
       </c>
@@ -12472,10 +14638,13 @@
         <v>247</v>
       </c>
       <c r="R299" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.4">
+        <v>902</v>
+      </c>
+      <c r="S299" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A300">
         <v>812</v>
       </c>
@@ -12504,10 +14673,13 @@
         <v>34</v>
       </c>
       <c r="R300" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.4">
+        <v>903</v>
+      </c>
+      <c r="S300" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A301">
         <v>813</v>
       </c>
@@ -12533,10 +14705,13 @@
         <v>20</v>
       </c>
       <c r="R301" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.4">
+        <v>904</v>
+      </c>
+      <c r="S301" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A302">
         <v>830</v>
       </c>
@@ -12562,10 +14737,13 @@
         <v>20</v>
       </c>
       <c r="R302" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.4">
+        <v>905</v>
+      </c>
+      <c r="S302" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A303">
         <v>833</v>
       </c>
@@ -12600,10 +14778,13 @@
         <v>43</v>
       </c>
       <c r="R303" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.4">
+        <v>906</v>
+      </c>
+      <c r="S303" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A304">
         <v>834</v>
       </c>
@@ -12638,10 +14819,13 @@
         <v>91</v>
       </c>
       <c r="R304" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.4">
+        <v>907</v>
+      </c>
+      <c r="S304" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A305">
         <v>838</v>
       </c>
@@ -12673,10 +14857,13 @@
         <v>193</v>
       </c>
       <c r="R305" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.4">
+        <v>908</v>
+      </c>
+      <c r="S305" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A306">
         <v>839</v>
       </c>
@@ -12711,10 +14898,13 @@
         <v>42</v>
       </c>
       <c r="R306" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.4">
+        <v>909</v>
+      </c>
+      <c r="S306" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A307">
         <v>841</v>
       </c>
@@ -12746,10 +14936,13 @@
         <v>42</v>
       </c>
       <c r="R307" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.4">
+        <v>910</v>
+      </c>
+      <c r="S307" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A308">
         <v>842</v>
       </c>
@@ -12781,10 +14974,13 @@
         <v>41</v>
       </c>
       <c r="R308" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.4">
+        <v>911</v>
+      </c>
+      <c r="S308" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A309">
         <v>844</v>
       </c>
@@ -12813,10 +15009,13 @@
         <v>20</v>
       </c>
       <c r="R309" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.4">
+        <v>620</v>
+      </c>
+      <c r="S309" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A310">
         <v>845</v>
       </c>
@@ -12842,10 +15041,13 @@
         <v>20</v>
       </c>
       <c r="R310" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.4">
+        <v>912</v>
+      </c>
+      <c r="S310" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A311">
         <v>848</v>
       </c>
@@ -12874,10 +15076,13 @@
         <v>20</v>
       </c>
       <c r="R311" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.4">
+        <v>913</v>
+      </c>
+      <c r="S311" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A312">
         <v>849</v>
       </c>
@@ -12906,10 +15111,13 @@
         <v>20</v>
       </c>
       <c r="R312" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.4">
+        <v>914</v>
+      </c>
+      <c r="S312" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A313">
         <v>850</v>
       </c>
@@ -12947,10 +15155,13 @@
         <v>28</v>
       </c>
       <c r="R313" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.4">
+        <v>915</v>
+      </c>
+      <c r="S313" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A314">
         <v>855</v>
       </c>
@@ -12976,10 +15187,13 @@
         <v>20</v>
       </c>
       <c r="R314" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.4">
+        <v>916</v>
+      </c>
+      <c r="S314" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A315">
         <v>857</v>
       </c>
@@ -13005,10 +15219,13 @@
         <v>20</v>
       </c>
       <c r="R315" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.4">
+        <v>917</v>
+      </c>
+      <c r="S315" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A316">
         <v>859</v>
       </c>
@@ -13034,10 +15251,13 @@
         <v>20</v>
       </c>
       <c r="R316" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.4">
+        <v>918</v>
+      </c>
+      <c r="S316" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A317">
         <v>861</v>
       </c>
@@ -13072,10 +15292,13 @@
         <v>28</v>
       </c>
       <c r="R317" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+      <c r="S317" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A318">
         <v>868</v>
       </c>
@@ -13101,10 +15324,13 @@
         <v>20</v>
       </c>
       <c r="R318" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.4">
+        <v>920</v>
+      </c>
+      <c r="S318" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A319">
         <v>870</v>
       </c>
@@ -13139,10 +15365,13 @@
         <v>91</v>
       </c>
       <c r="R319" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.4">
+        <v>921</v>
+      </c>
+      <c r="S319" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A320">
         <v>871</v>
       </c>
@@ -13168,10 +15397,13 @@
         <v>20</v>
       </c>
       <c r="R320" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="S320" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A321">
         <v>875</v>
       </c>
@@ -13203,10 +15435,13 @@
         <v>29</v>
       </c>
       <c r="R321" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.4">
+        <v>923</v>
+      </c>
+      <c r="S321" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A322">
         <v>885</v>
       </c>
@@ -13232,10 +15467,13 @@
         <v>34</v>
       </c>
       <c r="R322" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.4">
+        <v>924</v>
+      </c>
+      <c r="S322" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A323">
         <v>887</v>
       </c>
@@ -13261,10 +15499,13 @@
         <v>20</v>
       </c>
       <c r="R323" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.4">
+        <v>925</v>
+      </c>
+      <c r="S323" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A324">
         <v>901</v>
       </c>
@@ -13290,10 +15531,13 @@
         <v>20</v>
       </c>
       <c r="R324" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.4">
+        <v>926</v>
+      </c>
+      <c r="S324" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A325">
         <v>902</v>
       </c>
@@ -13319,10 +15563,13 @@
         <v>20</v>
       </c>
       <c r="R325" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.4">
+        <v>927</v>
+      </c>
+      <c r="S325" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A326">
         <v>903</v>
       </c>
@@ -13351,10 +15598,13 @@
         <v>43</v>
       </c>
       <c r="R326" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.4">
+        <v>928</v>
+      </c>
+      <c r="S326" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A327">
         <v>904</v>
       </c>
@@ -13383,10 +15633,13 @@
         <v>74</v>
       </c>
       <c r="R327" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.4">
+        <v>929</v>
+      </c>
+      <c r="S327" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A328">
         <v>906</v>
       </c>
@@ -13412,10 +15665,13 @@
         <v>20</v>
       </c>
       <c r="R328" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.4">
+        <v>930</v>
+      </c>
+      <c r="S328" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A329">
         <v>907</v>
       </c>
@@ -13441,10 +15697,13 @@
         <v>20</v>
       </c>
       <c r="R329" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.4">
+        <v>931</v>
+      </c>
+      <c r="S329" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A330">
         <v>908</v>
       </c>
@@ -13470,10 +15729,13 @@
         <v>20</v>
       </c>
       <c r="R330" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.4">
+        <v>932</v>
+      </c>
+      <c r="S330" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A331">
         <v>909</v>
       </c>
@@ -13499,10 +15761,13 @@
         <v>20</v>
       </c>
       <c r="R331" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.4">
+        <v>933</v>
+      </c>
+      <c r="S331" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A332">
         <v>913</v>
       </c>
@@ -13542,8 +15807,11 @@
       <c r="M332" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R332" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A333">
         <v>914</v>
       </c>
@@ -13569,10 +15837,13 @@
         <v>20</v>
       </c>
       <c r="R333" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.4">
+        <v>935</v>
+      </c>
+      <c r="S333" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A334">
         <v>917</v>
       </c>
@@ -13601,10 +15872,13 @@
         <v>20</v>
       </c>
       <c r="R334" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.4">
+        <v>675</v>
+      </c>
+      <c r="S334" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A335">
         <v>924</v>
       </c>
@@ -13636,10 +15910,13 @@
         <v>41</v>
       </c>
       <c r="R335" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.4">
+        <v>936</v>
+      </c>
+      <c r="S335" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A336">
         <v>935</v>
       </c>
@@ -13671,10 +15948,13 @@
         <v>21</v>
       </c>
       <c r="R336" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.4">
+        <v>937</v>
+      </c>
+      <c r="S336" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A337">
         <v>944</v>
       </c>
@@ -13703,10 +15983,13 @@
         <v>91</v>
       </c>
       <c r="R337" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.4">
+        <v>938</v>
+      </c>
+      <c r="S337" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A338">
         <v>947</v>
       </c>
@@ -13732,10 +16015,13 @@
         <v>20</v>
       </c>
       <c r="R338" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.4">
+        <v>939</v>
+      </c>
+      <c r="S338" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A339">
         <v>948</v>
       </c>
@@ -13761,10 +16047,13 @@
         <v>34</v>
       </c>
       <c r="R339" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.4">
+        <v>940</v>
+      </c>
+      <c r="S339" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A340">
         <v>949</v>
       </c>
@@ -13790,10 +16079,13 @@
         <v>20</v>
       </c>
       <c r="R340" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.4">
+        <v>941</v>
+      </c>
+      <c r="S340" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A341">
         <v>954</v>
       </c>
@@ -13819,10 +16111,13 @@
         <v>34</v>
       </c>
       <c r="R341" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.4">
+        <v>942</v>
+      </c>
+      <c r="S341" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A342">
         <v>955</v>
       </c>
@@ -13848,10 +16143,13 @@
         <v>34</v>
       </c>
       <c r="R342" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.4">
+        <v>943</v>
+      </c>
+      <c r="S342" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A343">
         <v>960</v>
       </c>
@@ -13877,10 +16175,13 @@
         <v>20</v>
       </c>
       <c r="R343" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.4">
+        <v>944</v>
+      </c>
+      <c r="S343" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A344">
         <v>961</v>
       </c>
@@ -13906,10 +16207,13 @@
         <v>20</v>
       </c>
       <c r="R344" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.4">
+        <v>945</v>
+      </c>
+      <c r="S344" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A345">
         <v>966</v>
       </c>
@@ -13935,10 +16239,13 @@
         <v>20</v>
       </c>
       <c r="R345" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.4">
+        <v>946</v>
+      </c>
+      <c r="S345" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A346">
         <v>967</v>
       </c>
@@ -13964,10 +16271,13 @@
         <v>20</v>
       </c>
       <c r="R346" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.4">
+        <v>947</v>
+      </c>
+      <c r="S346" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A347">
         <v>969</v>
       </c>
@@ -13993,10 +16303,13 @@
         <v>20</v>
       </c>
       <c r="R347" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.4">
+        <v>948</v>
+      </c>
+      <c r="S347" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A348">
         <v>970</v>
       </c>
@@ -14022,10 +16335,13 @@
         <v>20</v>
       </c>
       <c r="R348" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.4">
+        <v>949</v>
+      </c>
+      <c r="S348" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A349">
         <v>971</v>
       </c>
@@ -14051,10 +16367,13 @@
         <v>20</v>
       </c>
       <c r="R349" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.4">
+        <v>950</v>
+      </c>
+      <c r="S349" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A350">
         <v>976</v>
       </c>
@@ -14080,10 +16399,13 @@
         <v>20</v>
       </c>
       <c r="R350" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.4">
+        <v>951</v>
+      </c>
+      <c r="S350" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A351">
         <v>977</v>
       </c>
@@ -14109,10 +16431,13 @@
         <v>20</v>
       </c>
       <c r="R351" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.4">
+        <v>725</v>
+      </c>
+      <c r="S351" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A352">
         <v>981</v>
       </c>
@@ -14141,10 +16466,13 @@
         <v>20</v>
       </c>
       <c r="R352" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.4">
+        <v>952</v>
+      </c>
+      <c r="S352" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A353">
         <v>983</v>
       </c>
@@ -14188,10 +16516,13 @@
         <v>247</v>
       </c>
       <c r="R353" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.4">
+        <v>642</v>
+      </c>
+      <c r="S353" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A354">
         <v>984</v>
       </c>
@@ -14217,10 +16548,13 @@
         <v>20</v>
       </c>
       <c r="R354" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.4">
+        <v>953</v>
+      </c>
+      <c r="S354" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A355">
         <v>987</v>
       </c>
@@ -14261,10 +16595,13 @@
         <v>43</v>
       </c>
       <c r="R355" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.4">
+        <v>954</v>
+      </c>
+      <c r="S355" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="356" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A356">
         <v>988</v>
       </c>
@@ -14302,10 +16639,13 @@
         <v>42</v>
       </c>
       <c r="R356" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.4">
+        <v>955</v>
+      </c>
+      <c r="S356" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="357" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A357">
         <v>996</v>
       </c>
@@ -14340,10 +16680,13 @@
         <v>91</v>
       </c>
       <c r="R357" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.4">
+        <v>956</v>
+      </c>
+      <c r="S357" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="358" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A358">
         <v>997</v>
       </c>
@@ -14390,10 +16733,13 @@
         <v>247</v>
       </c>
       <c r="R358" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.4">
+        <v>957</v>
+      </c>
+      <c r="S358" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="359" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A359">
         <v>1000</v>
       </c>
@@ -14425,10 +16771,13 @@
         <v>91</v>
       </c>
       <c r="R359" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.4">
+        <v>958</v>
+      </c>
+      <c r="S359" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="360" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A360">
         <v>1003</v>
       </c>
@@ -14469,10 +16818,13 @@
         <v>247</v>
       </c>
       <c r="R360" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.4">
+        <v>959</v>
+      </c>
+      <c r="S360" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="361" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A361">
         <v>1004</v>
       </c>
@@ -14510,10 +16862,13 @@
         <v>91</v>
       </c>
       <c r="R361" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.4">
+        <v>960</v>
+      </c>
+      <c r="S361" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="362" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A362">
         <v>1007</v>
       </c>
@@ -14566,10 +16921,13 @@
         <v>73</v>
       </c>
       <c r="R362" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.4">
+        <v>961</v>
+      </c>
+      <c r="S362" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="363" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A363">
         <v>1009</v>
       </c>
@@ -14610,10 +16968,13 @@
         <v>247</v>
       </c>
       <c r="R363" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.4">
+        <v>962</v>
+      </c>
+      <c r="S363" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A364">
         <v>1011</v>
       </c>
@@ -14654,10 +17015,13 @@
         <v>247</v>
       </c>
       <c r="R364" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.4">
+        <v>963</v>
+      </c>
+      <c r="S364" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="365" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A365">
         <v>1012</v>
       </c>
@@ -14686,10 +17050,13 @@
         <v>20</v>
       </c>
       <c r="R365" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.4">
+        <v>964</v>
+      </c>
+      <c r="S365" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A366">
         <v>1013</v>
       </c>
@@ -14730,10 +17097,13 @@
         <v>42</v>
       </c>
       <c r="R366" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.4">
+        <v>965</v>
+      </c>
+      <c r="S366" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A367">
         <v>1014</v>
       </c>
@@ -14777,10 +17147,13 @@
         <v>42</v>
       </c>
       <c r="R367" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.4">
+        <v>966</v>
+      </c>
+      <c r="S367" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A368">
         <v>1032</v>
       </c>
@@ -14809,10 +17182,13 @@
         <v>34</v>
       </c>
       <c r="R368" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.4">
+        <v>967</v>
+      </c>
+      <c r="S368" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="369" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A369">
         <v>1033</v>
       </c>
@@ -14853,10 +17229,13 @@
         <v>247</v>
       </c>
       <c r="R369" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.4">
+        <v>968</v>
+      </c>
+      <c r="S369" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="370" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A370">
         <v>1049</v>
       </c>
@@ -14900,10 +17279,13 @@
         <v>247</v>
       </c>
       <c r="R370" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.4">
+        <v>969</v>
+      </c>
+      <c r="S370" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="371" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A371">
         <v>1058</v>
       </c>
@@ -14929,10 +17311,13 @@
         <v>76</v>
       </c>
       <c r="R371" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.4">
+        <v>970</v>
+      </c>
+      <c r="S371" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="372" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A372">
         <v>1059</v>
       </c>
@@ -14958,10 +17343,13 @@
         <v>76</v>
       </c>
       <c r="R372" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.4">
+        <v>971</v>
+      </c>
+      <c r="S372" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="373" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A373">
         <v>1060</v>
       </c>
@@ -14987,10 +17375,13 @@
         <v>76</v>
       </c>
       <c r="R373" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.4">
+        <v>972</v>
+      </c>
+      <c r="S373" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="374" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A374">
         <v>1066</v>
       </c>
@@ -15016,10 +17407,13 @@
         <v>20</v>
       </c>
       <c r="R374" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.4">
+        <v>973</v>
+      </c>
+      <c r="S374" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="375" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A375">
         <v>1070</v>
       </c>
@@ -15045,10 +17439,13 @@
         <v>20</v>
       </c>
       <c r="R375" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.4">
+        <v>974</v>
+      </c>
+      <c r="S375" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="376" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A376">
         <v>1076</v>
       </c>
@@ -15089,10 +17486,13 @@
         <v>247</v>
       </c>
       <c r="R376" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.4">
+        <v>975</v>
+      </c>
+      <c r="S376" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="377" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A377">
         <v>1087</v>
       </c>
@@ -15133,10 +17533,13 @@
         <v>247</v>
       </c>
       <c r="R377" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.4">
+        <v>976</v>
+      </c>
+      <c r="S377" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="378" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A378">
         <v>1088</v>
       </c>
@@ -15177,10 +17580,13 @@
         <v>247</v>
       </c>
       <c r="R378" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.4">
+        <v>977</v>
+      </c>
+      <c r="S378" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="379" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A379">
         <v>1100</v>
       </c>
@@ -15206,10 +17612,13 @@
         <v>34</v>
       </c>
       <c r="R379" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.4">
+        <v>978</v>
+      </c>
+      <c r="S379" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="380" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A380">
         <v>1111</v>
       </c>
@@ -15238,10 +17647,13 @@
         <v>34</v>
       </c>
       <c r="R380" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.4">
+        <v>979</v>
+      </c>
+      <c r="S380" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="381" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A381">
         <v>1113</v>
       </c>
@@ -15270,10 +17682,13 @@
         <v>20</v>
       </c>
       <c r="R381" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.4">
+        <v>980</v>
+      </c>
+      <c r="S381" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="382" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A382">
         <v>1114</v>
       </c>
@@ -15302,10 +17717,13 @@
         <v>20</v>
       </c>
       <c r="R382" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.4">
+        <v>981</v>
+      </c>
+      <c r="S382" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="383" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A383">
         <v>1147</v>
       </c>
@@ -15349,10 +17767,13 @@
         <v>247</v>
       </c>
       <c r="R383" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.4">
+        <v>982</v>
+      </c>
+      <c r="S383" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="384" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A384">
         <v>1170</v>
       </c>
@@ -15384,10 +17805,13 @@
         <v>42</v>
       </c>
       <c r="R384" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.4">
+        <v>983</v>
+      </c>
+      <c r="S384" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A385">
         <v>1173</v>
       </c>
@@ -15416,10 +17840,13 @@
         <v>20</v>
       </c>
       <c r="R385" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.4">
+        <v>984</v>
+      </c>
+      <c r="S385" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A386">
         <v>1186</v>
       </c>
@@ -15445,10 +17872,13 @@
         <v>164</v>
       </c>
       <c r="R386" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.4">
+        <v>985</v>
+      </c>
+      <c r="S386" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A387">
         <v>1187</v>
       </c>
@@ -15474,10 +17904,13 @@
         <v>34</v>
       </c>
       <c r="R387" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.4">
+        <v>986</v>
+      </c>
+      <c r="S387" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A388">
         <v>1188</v>
       </c>
@@ -15503,10 +17936,13 @@
         <v>20</v>
       </c>
       <c r="R388" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.4">
+        <v>987</v>
+      </c>
+      <c r="S388" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A389">
         <v>1189</v>
       </c>
@@ -15532,10 +17968,13 @@
         <v>20</v>
       </c>
       <c r="R389" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.4">
+        <v>988</v>
+      </c>
+      <c r="S389" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A390">
         <v>1257</v>
       </c>
@@ -15564,10 +18003,13 @@
         <v>34</v>
       </c>
       <c r="R390" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.4">
+        <v>623</v>
+      </c>
+      <c r="S390" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A391">
         <v>1260</v>
       </c>
@@ -15599,10 +18041,13 @@
         <v>73</v>
       </c>
       <c r="R391" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.4">
+        <v>989</v>
+      </c>
+      <c r="S391" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A392">
         <v>1266</v>
       </c>
@@ -15634,10 +18079,13 @@
         <v>85</v>
       </c>
       <c r="R392" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.4">
+        <v>990</v>
+      </c>
+      <c r="S392" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A393">
         <v>1267</v>
       </c>
@@ -15669,10 +18117,13 @@
         <v>41</v>
       </c>
       <c r="R393" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.4">
+        <v>767</v>
+      </c>
+      <c r="S393" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A394">
         <v>1276</v>
       </c>
@@ -15701,10 +18152,13 @@
         <v>21</v>
       </c>
       <c r="R394" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.4">
+        <v>991</v>
+      </c>
+      <c r="S394" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A395">
         <v>1284</v>
       </c>
@@ -15730,10 +18184,13 @@
         <v>34</v>
       </c>
       <c r="R395" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="396" spans="1:18" x14ac:dyDescent="0.4">
+        <v>992</v>
+      </c>
+      <c r="S395" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A396">
         <v>1290</v>
       </c>
@@ -15762,10 +18219,13 @@
         <v>20</v>
       </c>
       <c r="R396" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.4">
+        <v>993</v>
+      </c>
+      <c r="S396" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A397">
         <v>1296</v>
       </c>
@@ -15791,10 +18251,13 @@
         <v>34</v>
       </c>
       <c r="R397" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.4">
+        <v>994</v>
+      </c>
+      <c r="S397" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A398">
         <v>1297</v>
       </c>
@@ -15823,10 +18286,13 @@
         <v>20</v>
       </c>
       <c r="R398" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.4">
+        <v>874</v>
+      </c>
+      <c r="S398" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A399">
         <v>1308</v>
       </c>
@@ -15852,10 +18318,13 @@
         <v>20</v>
       </c>
       <c r="R399" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.4">
+        <v>995</v>
+      </c>
+      <c r="S399" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A400">
         <v>1309</v>
       </c>
@@ -15881,10 +18350,13 @@
         <v>20</v>
       </c>
       <c r="R400" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.4">
+        <v>612</v>
+      </c>
+      <c r="S400" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A401">
         <v>1327</v>
       </c>
@@ -15910,10 +18382,13 @@
         <v>34</v>
       </c>
       <c r="R401" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.4">
+        <v>996</v>
+      </c>
+      <c r="S401" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A402">
         <v>1329</v>
       </c>
@@ -15939,10 +18414,13 @@
         <v>20</v>
       </c>
       <c r="R402" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.4">
+        <v>623</v>
+      </c>
+      <c r="S402" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A403">
         <v>1334</v>
       </c>
@@ -15983,10 +18461,13 @@
         <v>22</v>
       </c>
       <c r="R403" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.4">
+        <v>997</v>
+      </c>
+      <c r="S403" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A404">
         <v>1341</v>
       </c>
@@ -16012,10 +18493,13 @@
         <v>20</v>
       </c>
       <c r="R404" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.4">
+        <v>998</v>
+      </c>
+      <c r="S404" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A405">
         <v>1342</v>
       </c>
@@ -16041,10 +18525,13 @@
         <v>20</v>
       </c>
       <c r="R405" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.4">
+        <v>999</v>
+      </c>
+      <c r="S405" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A406">
         <v>1343</v>
       </c>
@@ -16076,10 +18563,13 @@
         <v>43</v>
       </c>
       <c r="R406" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1000</v>
+      </c>
+      <c r="S406" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A407">
         <v>1346</v>
       </c>
@@ -16105,10 +18595,13 @@
         <v>20</v>
       </c>
       <c r="R407" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1001</v>
+      </c>
+      <c r="S407" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A408">
         <v>1349</v>
       </c>
@@ -16134,10 +18627,13 @@
         <v>20</v>
       </c>
       <c r="R408" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="409" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1002</v>
+      </c>
+      <c r="S408" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A409">
         <v>1350</v>
       </c>
@@ -16163,10 +18659,13 @@
         <v>20</v>
       </c>
       <c r="R409" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1003</v>
+      </c>
+      <c r="S409" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A410">
         <v>1351</v>
       </c>
@@ -16192,10 +18691,13 @@
         <v>20</v>
       </c>
       <c r="R410" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1004</v>
+      </c>
+      <c r="S410" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A411">
         <v>1352</v>
       </c>
@@ -16221,10 +18723,13 @@
         <v>20</v>
       </c>
       <c r="R411" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1005</v>
+      </c>
+      <c r="S411" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A412">
         <v>1353</v>
       </c>
@@ -16250,10 +18755,13 @@
         <v>34</v>
       </c>
       <c r="R412" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1006</v>
+      </c>
+      <c r="S412" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A413">
         <v>1354</v>
       </c>
@@ -16279,10 +18787,13 @@
         <v>20</v>
       </c>
       <c r="R413" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1007</v>
+      </c>
+      <c r="S413" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A414">
         <v>1355</v>
       </c>
@@ -16308,10 +18819,13 @@
         <v>34</v>
       </c>
       <c r="R414" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.4">
+        <v>612</v>
+      </c>
+      <c r="S414" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A415">
         <v>1356</v>
       </c>
@@ -16337,10 +18851,13 @@
         <v>20</v>
       </c>
       <c r="R415" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1008</v>
+      </c>
+      <c r="S415" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="416" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A416">
         <v>1357</v>
       </c>
@@ -16366,10 +18883,13 @@
         <v>20</v>
       </c>
       <c r="R416" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1009</v>
+      </c>
+      <c r="S416" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="417" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A417">
         <v>1358</v>
       </c>
@@ -16398,10 +18918,13 @@
         <v>247</v>
       </c>
       <c r="R417" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.4">
+        <v>734</v>
+      </c>
+      <c r="S417" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="418" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A418">
         <v>1368</v>
       </c>
@@ -16430,10 +18953,13 @@
         <v>20</v>
       </c>
       <c r="R418" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1004</v>
+      </c>
+      <c r="S418" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="419" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A419">
         <v>1385</v>
       </c>
@@ -16459,10 +18985,13 @@
         <v>20</v>
       </c>
       <c r="R419" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.4">
+        <v>664</v>
+      </c>
+      <c r="S419" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="420" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A420">
         <v>1404</v>
       </c>
@@ -16491,10 +19020,13 @@
         <v>20</v>
       </c>
       <c r="R420" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1010</v>
+      </c>
+      <c r="S420" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="421" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A421">
         <v>1411</v>
       </c>
@@ -16526,10 +19058,13 @@
         <v>193</v>
       </c>
       <c r="R421" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1011</v>
+      </c>
+      <c r="S421" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="422" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A422">
         <v>1497</v>
       </c>
@@ -16570,10 +19105,13 @@
         <v>91</v>
       </c>
       <c r="R422" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1012</v>
+      </c>
+      <c r="S422" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="423" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A423">
         <v>1508</v>
       </c>
@@ -16599,10 +19137,13 @@
         <v>34</v>
       </c>
       <c r="R423" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1013</v>
+      </c>
+      <c r="S423" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="424" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A424">
         <v>1512</v>
       </c>
@@ -16628,10 +19169,13 @@
         <v>34</v>
       </c>
       <c r="R424" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1014</v>
+      </c>
+      <c r="S424" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="425" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A425">
         <v>1513</v>
       </c>
@@ -16657,10 +19201,13 @@
         <v>20</v>
       </c>
       <c r="R425" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1015</v>
+      </c>
+      <c r="S425" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="426" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A426">
         <v>1513</v>
       </c>
@@ -16686,10 +19233,13 @@
         <v>20</v>
       </c>
       <c r="R426" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1016</v>
+      </c>
+      <c r="S426" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="427" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A427">
         <v>1551</v>
       </c>
@@ -16721,10 +19271,13 @@
         <v>42</v>
       </c>
       <c r="R427" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1017</v>
+      </c>
+      <c r="S427" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="428" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A428">
         <v>1552</v>
       </c>
@@ -16750,10 +19303,13 @@
         <v>20</v>
       </c>
       <c r="R428" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.4">
+        <v>854</v>
+      </c>
+      <c r="S428" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="429" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A429">
         <v>1553</v>
       </c>
@@ -16779,10 +19335,13 @@
         <v>34</v>
       </c>
       <c r="R429" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1018</v>
+      </c>
+      <c r="S429" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="430" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A430">
         <v>1554</v>
       </c>
@@ -16808,10 +19367,13 @@
         <v>20</v>
       </c>
       <c r="R430" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1019</v>
+      </c>
+      <c r="S430" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="431" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A431">
         <v>1568</v>
       </c>
@@ -16837,10 +19399,13 @@
         <v>20</v>
       </c>
       <c r="R431" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1020</v>
+      </c>
+      <c r="S431" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="432" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A432">
         <v>1578</v>
       </c>
@@ -16869,10 +19434,13 @@
         <v>21</v>
       </c>
       <c r="R432" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1021</v>
+      </c>
+      <c r="S432" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="433" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A433">
         <v>1624</v>
       </c>
@@ -16901,10 +19469,13 @@
         <v>76</v>
       </c>
       <c r="R433" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1022</v>
+      </c>
+      <c r="S433" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="434" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A434">
         <v>1635</v>
       </c>
@@ -16933,10 +19504,13 @@
         <v>20</v>
       </c>
       <c r="R434" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1023</v>
+      </c>
+      <c r="S434" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="435" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A435">
         <v>1636</v>
       </c>
@@ -16965,10 +19539,13 @@
         <v>20</v>
       </c>
       <c r="R435" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1024</v>
+      </c>
+      <c r="S435" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="436" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A436">
         <v>1641</v>
       </c>
@@ -16994,10 +19571,13 @@
         <v>20</v>
       </c>
       <c r="R436" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1025</v>
+      </c>
+      <c r="S436" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A437">
         <v>1678</v>
       </c>
@@ -17023,10 +19603,13 @@
         <v>20</v>
       </c>
       <c r="R437" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1026</v>
+      </c>
+      <c r="S437" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A438">
         <v>1695</v>
       </c>
@@ -17055,10 +19638,13 @@
         <v>34</v>
       </c>
       <c r="R438" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1027</v>
+      </c>
+      <c r="S438" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="439" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A439">
         <v>1696</v>
       </c>
@@ -17087,10 +19673,13 @@
         <v>20</v>
       </c>
       <c r="R439" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1028</v>
+      </c>
+      <c r="S439" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A440">
         <v>1702</v>
       </c>
@@ -17116,10 +19705,13 @@
         <v>34</v>
       </c>
       <c r="R440" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1029</v>
+      </c>
+      <c r="S440" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="441" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A441">
         <v>1703</v>
       </c>
@@ -17145,10 +19737,13 @@
         <v>20</v>
       </c>
       <c r="R441" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1030</v>
+      </c>
+      <c r="S441" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="442" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A442">
         <v>1704</v>
       </c>
@@ -17177,10 +19772,13 @@
         <v>34</v>
       </c>
       <c r="R442" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1031</v>
+      </c>
+      <c r="S442" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="443" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A443">
         <v>1713</v>
       </c>
@@ -17209,10 +19807,13 @@
         <v>20</v>
       </c>
       <c r="R443" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1032</v>
+      </c>
+      <c r="S443" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="444" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A444">
         <v>1717</v>
       </c>
@@ -17241,10 +19842,13 @@
         <v>34</v>
       </c>
       <c r="R444" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1033</v>
+      </c>
+      <c r="S444" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="445" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A445">
         <v>1718</v>
       </c>
@@ -17273,10 +19877,13 @@
         <v>20</v>
       </c>
       <c r="R445" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1034</v>
+      </c>
+      <c r="S445" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="446" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A446">
         <v>1737</v>
       </c>
@@ -17305,10 +19912,13 @@
         <v>20</v>
       </c>
       <c r="R446" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1035</v>
+      </c>
+      <c r="S446" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="447" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A447">
         <v>1738</v>
       </c>
@@ -17337,10 +19947,13 @@
         <v>20</v>
       </c>
       <c r="R447" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.4">
+        <v>1036</v>
+      </c>
+      <c r="S447" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="448" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A448">
         <v>1739</v>
       </c>
@@ -17368,11 +19981,11 @@
       <c r="I448" t="s">
         <v>20</v>
       </c>
-      <c r="R448" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S448" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="449" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A449">
         <v>1740</v>
       </c>
@@ -17400,11 +20013,11 @@
       <c r="I449" t="s">
         <v>34</v>
       </c>
-      <c r="R449" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S449" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="450" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A450">
         <v>1742</v>
       </c>
@@ -17432,11 +20045,11 @@
       <c r="I450" t="s">
         <v>20</v>
       </c>
-      <c r="R450" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S450" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="451" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A451">
         <v>1771</v>
       </c>
@@ -17467,11 +20080,11 @@
       <c r="J451" t="s">
         <v>29</v>
       </c>
-      <c r="R451" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S451" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="452" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A452">
         <v>1792</v>
       </c>
@@ -17502,11 +20115,11 @@
       <c r="J452" t="s">
         <v>91</v>
       </c>
-      <c r="R452" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S452" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="453" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A453">
         <v>1818</v>
       </c>
@@ -17537,11 +20150,11 @@
       <c r="J453" t="s">
         <v>73</v>
       </c>
-      <c r="R453" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="S453" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="454" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A454">
         <v>1821</v>
       </c>
@@ -17567,7 +20180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A455">
         <v>1822</v>
       </c>
